--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>NSYS</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E8" s="3">
         <v>35000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>52300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>27400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>30100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>29000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E9" s="3">
         <v>29500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24700</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>23400</v>
       </c>
       <c r="Z9" s="3">
         <v>23400</v>
       </c>
       <c r="AA9" s="3">
+        <v>23400</v>
+      </c>
+      <c r="AB9" s="3">
         <v>24800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>25500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="E10" s="3">
         <v>5500</v>
       </c>
       <c r="F10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G10" s="3">
         <v>5100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1099,25 +1113,25 @@
         <v>300</v>
       </c>
       <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>100</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
       </c>
       <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
         <v>200</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1273,8 +1293,8 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1286,25 +1306,25 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-6200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1321,8 +1341,8 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1330,20 +1350,20 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>200</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E17" s="3">
         <v>33900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>30000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>27300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>30200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>28200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>28700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E18" s="3">
         <v>1100</v>
       </c>
       <c r="F18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>800</v>
       </c>
       <c r="S18" s="3">
         <v>800</v>
       </c>
       <c r="T18" s="3">
+        <v>800</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="X18" s="3">
         <v>700</v>
       </c>
       <c r="Y18" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1717,13 +1751,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1782,85 +1819,88 @@
         <v>1600</v>
       </c>
       <c r="F21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-700</v>
-      </c>
-      <c r="U21" s="3">
-        <v>500</v>
       </c>
       <c r="V21" s="3">
         <v>500</v>
       </c>
       <c r="W21" s="3">
+        <v>500</v>
+      </c>
+      <c r="X21" s="3">
         <v>1200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1889,25 +1929,25 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
-      </c>
-      <c r="P22" s="3">
-        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
       </c>
       <c r="R22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>300</v>
@@ -1916,7 +1956,7 @@
         <v>300</v>
       </c>
       <c r="U22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
@@ -1937,7 +1977,7 @@
         <v>200</v>
       </c>
       <c r="AB22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
@@ -1948,8 +1988,11 @@
       <c r="AE22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1957,150 +2000,153 @@
         <v>1000</v>
       </c>
       <c r="E23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
-      </c>
-      <c r="W23" s="3">
-        <v>500</v>
       </c>
       <c r="X23" s="3">
         <v>500</v>
       </c>
       <c r="Y23" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
       </c>
       <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
@@ -2109,25 +2155,28 @@
         <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,83 +2264,86 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>400</v>
       </c>
       <c r="X26" s="3">
         <v>400</v>
       </c>
       <c r="Y26" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
         <v>0</v>
       </c>
@@ -2299,88 +2351,91 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>400</v>
       </c>
       <c r="X27" s="3">
         <v>400</v>
       </c>
       <c r="Y27" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
         <v>0</v>
       </c>
@@ -2388,13 +2443,16 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2535,17 +2596,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2553,11 +2614,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2785,13 +2855,13 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2838,83 +2908,86 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>400</v>
       </c>
       <c r="X33" s="3">
         <v>400</v>
       </c>
       <c r="Y33" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
         <v>0</v>
       </c>
@@ -2922,13 +2995,16 @@
         <v>0</v>
       </c>
       <c r="AD33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,83 +3092,86 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>400</v>
       </c>
       <c r="X35" s="3">
         <v>400</v>
       </c>
       <c r="Y35" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
         <v>0</v>
       </c>
@@ -3100,107 +3179,113 @@
         <v>0</v>
       </c>
       <c r="AD35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,76 +3351,77 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
-      </c>
-      <c r="M41" s="3">
-        <v>400</v>
       </c>
       <c r="N41" s="3">
         <v>400</v>
       </c>
       <c r="O41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P41" s="3">
         <v>300</v>
       </c>
       <c r="Q41" s="3">
+        <v>300</v>
+      </c>
+      <c r="R41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>500</v>
-      </c>
-      <c r="W41" s="3">
-        <v>400</v>
       </c>
       <c r="X41" s="3">
         <v>400</v>
       </c>
       <c r="Y41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z41" s="3">
         <v>500</v>
@@ -3343,19 +3430,22 @@
         <v>500</v>
       </c>
       <c r="AB41" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AC41" s="3">
         <v>200</v>
       </c>
       <c r="AD41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE41" s="3">
         <v>300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,364 +3533,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E43" s="3">
         <v>29000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>30600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>26200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>24300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>18600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>17500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E44" s="3">
         <v>21100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>22400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>17100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>15500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>15400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>16900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>16300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>16000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>15200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>14000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>21100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>21600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>21700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>20700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2400</v>
       </c>
       <c r="M45" s="3">
         <v>2400</v>
       </c>
       <c r="N45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O45" s="3">
         <v>5200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>2400</v>
       </c>
       <c r="R45" s="3">
         <v>2400</v>
       </c>
       <c r="S45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T45" s="3">
         <v>3800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E46" s="3">
         <v>54400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>58100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>52800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>46200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>40800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>45500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>43300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>48300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>50500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>43300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>41800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>39100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>37800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>40700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>40300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>39500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,70 +3993,73 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E48" s="3">
         <v>13700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>14600</v>
       </c>
       <c r="I48" s="3">
         <v>14600</v>
       </c>
       <c r="J48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K48" s="3">
         <v>14800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>14700</v>
       </c>
       <c r="T48" s="3">
         <v>14700</v>
       </c>
       <c r="U48" s="3">
+        <v>14700</v>
+      </c>
+      <c r="V48" s="3">
         <v>15300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10200</v>
-      </c>
-      <c r="W48" s="3">
-        <v>10100</v>
       </c>
       <c r="X48" s="3">
         <v>10100</v>
@@ -3960,25 +4068,28 @@
         <v>10100</v>
       </c>
       <c r="Z48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AA48" s="3">
         <v>10200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3986,7 +4097,7 @@
         <v>300</v>
       </c>
       <c r="E49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F49" s="3">
         <v>400</v>
@@ -3995,7 +4106,7 @@
         <v>400</v>
       </c>
       <c r="H49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I49" s="3">
         <v>500</v>
@@ -4007,28 +4118,28 @@
         <v>500</v>
       </c>
       <c r="L49" s="3">
+        <v>500</v>
+      </c>
+      <c r="M49" s="3">
         <v>1100</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1200</v>
       </c>
       <c r="N49" s="3">
         <v>1200</v>
       </c>
       <c r="O49" s="3">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="P49" s="3">
         <v>3600</v>
       </c>
       <c r="Q49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="R49" s="3">
         <v>3700</v>
       </c>
       <c r="S49" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="T49" s="3">
         <v>3800</v>
@@ -4037,37 +4148,40 @@
         <v>3800</v>
       </c>
       <c r="V49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W49" s="3">
         <v>3900</v>
-      </c>
-      <c r="W49" s="3">
-        <v>4000</v>
       </c>
       <c r="X49" s="3">
         <v>4000</v>
       </c>
       <c r="Y49" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="Z49" s="3">
         <v>4100</v>
       </c>
       <c r="AA49" s="3">
-        <v>5100</v>
+        <v>4100</v>
       </c>
       <c r="AB49" s="3">
         <v>5100</v>
       </c>
       <c r="AC49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AD49" s="3">
         <v>5200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4270,17 +4390,17 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="L52" s="3">
-        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
+      <c r="N52" s="3">
+        <v>400</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>8</v>
@@ -4291,8 +4411,8 @@
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -4319,10 +4439,10 @@
         <v>0</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>500</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>600</v>
       </c>
       <c r="AC52" s="3">
         <v>600</v>
@@ -4331,10 +4451,13 @@
         <v>600</v>
       </c>
       <c r="AE52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E54" s="3">
         <v>68400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>67900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>60000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>61100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>63100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>61400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>65300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>69700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>55900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>53300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>52100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>55900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>55800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>55500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4707,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E57" s="3">
         <v>15300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>11200</v>
       </c>
       <c r="O57" s="3">
         <v>11200</v>
       </c>
       <c r="P57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>13500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>21100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14800</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>15300</v>
       </c>
       <c r="AC57" s="3">
         <v>15300</v>
       </c>
       <c r="AD57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>13800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4687,25 +4821,25 @@
         <v>400</v>
       </c>
       <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1900</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1100</v>
       </c>
       <c r="P58" s="3">
         <v>1100</v>
@@ -4714,40 +4848,40 @@
         <v>1100</v>
       </c>
       <c r="R58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S58" s="3">
         <v>1000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>1300</v>
       </c>
       <c r="Z58" s="3">
         <v>1300</v>
       </c>
       <c r="AA58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>1600</v>
       </c>
       <c r="AD58" s="3">
         <v>1600</v>
@@ -4755,79 +4889,82 @@
       <c r="AE58" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E59" s="3">
         <v>8700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5100</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>5000</v>
       </c>
       <c r="AA59" s="3">
         <v>5000</v>
@@ -4836,194 +4973,203 @@
         <v>5000</v>
       </c>
       <c r="AC59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AD59" s="3">
         <v>3900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E60" s="3">
         <v>24400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>28100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>18000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E61" s="3">
         <v>7400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10600</v>
-      </c>
-      <c r="P61" s="3">
-        <v>14900</v>
       </c>
       <c r="Q61" s="3">
         <v>14900</v>
       </c>
       <c r="R61" s="3">
+        <v>14900</v>
+      </c>
+      <c r="S61" s="3">
         <v>14700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5031,88 +5177,91 @@
         <v>7200</v>
       </c>
       <c r="E62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F62" s="3">
         <v>7400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9500</v>
-      </c>
-      <c r="N62" s="3">
-        <v>9000</v>
       </c>
       <c r="O62" s="3">
         <v>9000</v>
       </c>
       <c r="P62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>100</v>
-      </c>
-      <c r="W62" s="3">
-        <v>200</v>
       </c>
       <c r="X62" s="3">
         <v>200</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
       </c>
       <c r="AA62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB62" s="3">
         <v>400</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>600</v>
       </c>
       <c r="AC62" s="3">
         <v>600</v>
       </c>
       <c r="AD62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E66" s="3">
         <v>38900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>41000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>41100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>43000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,82 +6027,85 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E72" s="3">
         <v>13100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>6300</v>
       </c>
       <c r="AB72" s="3">
         <v>6300</v>
@@ -5943,10 +6117,13 @@
         <v>6300</v>
       </c>
       <c r="AE72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AF72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E76" s="3">
         <v>29200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>27800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21900</v>
-      </c>
-      <c r="P76" s="3">
-        <v>19800</v>
       </c>
       <c r="Q76" s="3">
         <v>19800</v>
       </c>
       <c r="R76" s="3">
+        <v>19800</v>
+      </c>
+      <c r="S76" s="3">
         <v>19700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22100</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>22000</v>
       </c>
       <c r="AC76" s="3">
         <v>22000</v>
       </c>
       <c r="AD76" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AE76" s="3">
         <v>22100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,177 +6579,183 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>400</v>
       </c>
       <c r="X81" s="3">
         <v>400</v>
       </c>
       <c r="Y81" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
         <v>0</v>
       </c>
@@ -6568,13 +6763,16 @@
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6630,22 +6829,22 @@
         <v>500</v>
       </c>
       <c r="J83" s="3">
+        <v>500</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
       </c>
       <c r="O83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>600</v>
@@ -6660,13 +6859,13 @@
         <v>600</v>
       </c>
       <c r="T83" s="3">
+        <v>600</v>
+      </c>
+      <c r="U83" s="3">
         <v>500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>500</v>
       </c>
       <c r="W83" s="3">
         <v>500</v>
@@ -6675,7 +6874,7 @@
         <v>500</v>
       </c>
       <c r="Y83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z83" s="3">
         <v>600</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,64 +7482,65 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-500</v>
       </c>
       <c r="F91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-200</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-400</v>
       </c>
       <c r="V91" s="3">
         <v>-400</v>
@@ -7328,13 +7549,13 @@
         <v>-400</v>
       </c>
       <c r="X91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
       <c r="Z91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AA91" s="3">
         <v>-200</v>
@@ -7346,13 +7567,16 @@
         <v>-200</v>
       </c>
       <c r="AD91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AE91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,64 +7756,67 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
         <v>-500</v>
       </c>
       <c r="F94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-400</v>
       </c>
       <c r="V94" s="3">
         <v>-400</v>
@@ -7595,7 +7825,7 @@
         <v>-400</v>
       </c>
       <c r="X94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Y94" s="3">
         <v>-300</v>
@@ -7604,22 +7834,25 @@
         <v>-300</v>
       </c>
       <c r="AA94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AB94" s="3">
         <v>-200</v>
       </c>
       <c r="AC94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD94" s="3">
         <v>400</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-300</v>
       </c>
       <c r="AE94" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-100</v>
       </c>
       <c r="Q100" s="3">
         <v>-100</v>
       </c>
       <c r="R100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S100" s="3">
         <v>-2600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-300</v>
       </c>
       <c r="Z100" s="3">
         <v>-300</v>
       </c>
       <c r="AA100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8107,8 +8356,8 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>8</v>
@@ -8116,11 +8365,11 @@
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -8128,11 +8377,11 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
@@ -8140,8 +8389,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8162,11 +8411,11 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -8179,99 +8428,105 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>8</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>NSYS</t>
   </si>
@@ -656,324 +656,343 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>36100</v>
+      </c>
+      <c r="F8" s="3">
         <v>33400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>35000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>34900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>35600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>35300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>32500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>30700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>33500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>29500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>52300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>22100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>23800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>26400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>26500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>27400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>30800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>30100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>27300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>28200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>28800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>29600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>28500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>26400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>25600</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>28300</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>30100</v>
       </c>
       <c r="AD8" s="3">
         <v>28300</v>
       </c>
       <c r="AE8" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AG8" s="3">
         <v>29000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F9" s="3">
         <v>28100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>29500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>29400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>30500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>28900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>27500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>26700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>30800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>21400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>47100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>20500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>22100</v>
-      </c>
-      <c r="P9" s="3">
-        <v>24400</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>24000</v>
       </c>
       <c r="R9" s="3">
         <v>24400</v>
       </c>
       <c r="S9" s="3">
+        <v>24000</v>
+      </c>
+      <c r="T9" s="3">
+        <v>24400</v>
+      </c>
+      <c r="U9" s="3">
         <v>27200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>26400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>25000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>25200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>25700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>26200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>24700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>23400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>23400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>24800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>26800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>25200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>25500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -981,91 +1000,97 @@
         <v>5400</v>
       </c>
       <c r="E10" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G10" s="3">
         <v>5500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>5100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>3800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1116,28 +1143,28 @@
         <v>300</v>
       </c>
       <c r="H12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,11 +1335,11 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1309,28 +1348,28 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-6200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1344,38 +1383,44 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>200</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>33400</v>
+      </c>
+      <c r="F17" s="3">
         <v>32200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>33900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>33800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>34900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>33300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>31500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>30500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>28200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>24500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>54000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>24200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>27600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>26400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>27000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>30000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>29300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>28500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>28300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>28800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>28900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>27800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>26600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>27300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>28000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>30200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>28200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>28700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F18" s="3">
         <v>1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1754,17 +1821,17 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1807,8 +1874,14 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,96 +1889,102 @@
         <v>1600</v>
       </c>
       <c r="E21" s="3">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="F21" s="3">
         <v>1600</v>
       </c>
       <c r="G21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>5500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1932,7 +2011,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1941,28 +2020,28 @@
         <v>200</v>
       </c>
       <c r="P22" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
       </c>
       <c r="R22" s="3">
+        <v>300</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>300</v>
-      </c>
       <c r="T22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>300</v>
       </c>
       <c r="V22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
@@ -1980,10 +2059,10 @@
         <v>200</v>
       </c>
       <c r="AC22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>100</v>
@@ -1991,8 +2070,14 @@
       <c r="AF22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2000,183 +2085,195 @@
         <v>1000</v>
       </c>
       <c r="E23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="3">
         <v>900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1100</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="J24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
       </c>
       <c r="AA24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
       <c r="AD26" s="3">
         <v>0</v>
       </c>
       <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
       <c r="AD27" s="3">
         <v>0</v>
       </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,32 +2720,32 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>-300</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>-300</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2858,17 +2997,17 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
       <c r="AD33" s="3">
         <v>0</v>
       </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
       <c r="AD35" s="3">
         <v>0</v>
       </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1000</v>
       </c>
       <c r="H41" s="3">
         <v>1300</v>
       </c>
       <c r="I41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
-      </c>
-      <c r="L41" s="3">
-        <v>400</v>
-      </c>
-      <c r="M41" s="3">
-        <v>700</v>
       </c>
       <c r="N41" s="3">
         <v>400</v>
       </c>
       <c r="O41" s="3">
+        <v>700</v>
+      </c>
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
+        <v>400</v>
+      </c>
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
-      </c>
-      <c r="S41" s="3">
-        <v>400</v>
-      </c>
-      <c r="T41" s="3">
-        <v>200</v>
       </c>
       <c r="U41" s="3">
         <v>400</v>
       </c>
       <c r="V41" s="3">
+        <v>200</v>
+      </c>
+      <c r="W41" s="3">
+        <v>400</v>
+      </c>
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>400</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>500</v>
       </c>
       <c r="AB41" s="3">
         <v>500</v>
       </c>
       <c r="AC41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,376 +3715,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>33800</v>
+      </c>
+      <c r="F43" s="3">
         <v>28100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>29000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>29700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>28600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>30600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>30700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>28000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>28500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>27300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>24800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>20500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>21500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>23400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>25600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>27000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>26200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>27300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>27900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>31700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>26500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>26100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>25900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>24300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>17600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>18600</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>17500</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>17300</v>
       </c>
       <c r="AE43" s="3">
         <v>17500</v>
       </c>
       <c r="AF43" s="3">
+        <v>17300</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="AH43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F44" s="3">
         <v>21500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>21100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>21300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>22400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>23600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>23000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>21200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>19400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>20600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>18300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>17100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>13900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>14500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>15500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>15400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>14300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>16900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>16300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>16000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>17000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>15200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>14000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>13000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>18500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>21100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>21600</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>21700</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>20700</v>
       </c>
       <c r="AF44" s="3">
         <v>21700</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>20700</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>21700</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F45" s="3">
         <v>2300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3200</v>
       </c>
       <c r="L45" s="3">
         <v>2800</v>
       </c>
       <c r="M45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>58800</v>
+      </c>
+      <c r="F46" s="3">
         <v>52600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>54400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>55600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>54900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>58100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>56500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>52800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>51800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>51100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>46200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>40400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>41000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>40800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>43600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>45500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>43300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>48300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>46800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>50500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>45900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>43300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>41800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>39100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>37800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>41800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>40700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>40300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>39500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,123 +4205,135 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F48" s="3">
         <v>13100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>14500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>14600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>14900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>15100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>15500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>15400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>13800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>14000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>14700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>15300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>10200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>10100</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>10100</v>
       </c>
       <c r="Z48" s="3">
         <v>10100</v>
       </c>
       <c r="AA48" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="AB48" s="3">
         <v>10100</v>
       </c>
       <c r="AC48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AE48" s="3">
         <v>9500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>9700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>10300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
         <v>300</v>
       </c>
       <c r="F49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H49" s="3">
         <v>400</v>
       </c>
       <c r="I49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K49" s="3">
         <v>500</v>
@@ -4121,58 +4342,58 @@
         <v>500</v>
       </c>
       <c r="M49" s="3">
+        <v>500</v>
+      </c>
+      <c r="N49" s="3">
+        <v>500</v>
+      </c>
+      <c r="O49" s="3">
         <v>1100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>3800</v>
-      </c>
-      <c r="U49" s="3">
-        <v>3800</v>
       </c>
       <c r="V49" s="3">
         <v>3800</v>
       </c>
       <c r="W49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y49" s="3">
         <v>3900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>5100</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>5200</v>
       </c>
       <c r="AE49" s="3">
         <v>5100</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,49 +4597,55 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>2600</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>400</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
@@ -4414,11 +4653,11 @@
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -4442,22 +4681,28 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>500</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>600</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>600</v>
       </c>
       <c r="AE52" s="3">
         <v>600</v>
       </c>
       <c r="AF52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>75100</v>
+      </c>
+      <c r="F54" s="3">
         <v>66000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>68400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>70100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>69500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>73100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>71500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>67900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>67100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>66500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>62800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>57500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>57600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>60000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>61100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>63100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>61400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>66800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>65300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>69700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>60000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>57400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>55900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>53300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>52100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>57500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>55900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>55800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>55500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,105 +4967,113 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>13100</v>
+        <v>15200</v>
       </c>
       <c r="E57" s="3">
-        <v>15300</v>
+        <v>15900</v>
       </c>
       <c r="F57" s="3">
         <v>13100</v>
       </c>
       <c r="G57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="H57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I57" s="3">
         <v>14800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>14700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>14000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>12700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>14100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>11200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>13500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>16400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>14000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>18400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>16800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>21100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>18100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>16900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>15700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>12100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>11700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>14800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>15300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>15300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>13800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -4824,444 +5091,474 @@
         <v>400</v>
       </c>
       <c r="J58" s="3">
+        <v>400</v>
+      </c>
+      <c r="K58" s="3">
+        <v>400</v>
+      </c>
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>9800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>11400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1100</v>
       </c>
       <c r="R58" s="3">
         <v>1100</v>
       </c>
       <c r="S58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U58" s="3">
         <v>1000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>900</v>
-      </c>
-      <c r="U58" s="3">
-        <v>1200</v>
       </c>
       <c r="V58" s="3">
         <v>900</v>
       </c>
       <c r="W58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X58" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>1600</v>
       </c>
       <c r="AF58" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F59" s="3">
         <v>9700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>14000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>11500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>9700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>10200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>9000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>8900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>7300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>7100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>6400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>7200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>6300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>6700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6100</v>
-      </c>
-      <c r="W59" s="3">
-        <v>5600</v>
-      </c>
-      <c r="X59" s="3">
-        <v>5000</v>
       </c>
       <c r="Y59" s="3">
         <v>5600</v>
       </c>
       <c r="Z59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AB59" s="3">
         <v>5100</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>5000</v>
       </c>
       <c r="AC59" s="3">
         <v>5000</v>
       </c>
       <c r="AD59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AF59" s="3">
         <v>3900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>26600</v>
+      </c>
+      <c r="F60" s="3">
         <v>23200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>24400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>27400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>26400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>26600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>24300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>24700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>22300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>32900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>31400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>19500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>18200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>21900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>23800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>22200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>25600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>24800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>28100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>24900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>23100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>22700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>18400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>18000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>20900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>21400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>20800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>20300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>7400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>6300</v>
       </c>
       <c r="G61" s="3">
         <v>7400</v>
       </c>
       <c r="H61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J61" s="3">
         <v>10500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>12100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>9900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>8200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>10600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>14900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>14900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>14700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>16900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>16500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>15700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>13800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>12800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>12100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>14000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>14100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>13900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>11500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>12000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>12200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7200</v>
+        <v>7400</v>
       </c>
       <c r="E62" s="3">
         <v>7200</v>
       </c>
       <c r="F62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H62" s="3">
         <v>7400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>7600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>7900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>8200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>8800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>8900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>9500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>9000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>9000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F66" s="3">
         <v>35300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>38900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>41200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>41500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>44900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>44600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>41000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>45500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>45400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>40300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>38900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>37800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>41100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>43000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>41400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>47100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>46100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>48700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>38900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>36100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>34900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>32500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>32300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>35200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>33600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>33500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>33200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,88 +6371,94 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F72" s="3">
         <v>14300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>13100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>12500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>11800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>12200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>10700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>10000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>6200</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>4200</v>
-      </c>
-      <c r="R72" s="3">
-        <v>4300</v>
       </c>
       <c r="S72" s="3">
         <v>4200</v>
       </c>
       <c r="T72" s="3">
+        <v>4300</v>
+      </c>
+      <c r="U72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V72" s="3">
         <v>3900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>5100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>5400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>5600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>5300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>4900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>6300</v>
       </c>
       <c r="AD72" s="3">
         <v>6300</v>
@@ -6120,10 +6467,16 @@
         <v>6300</v>
       </c>
       <c r="AF72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AH72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>35100</v>
+      </c>
+      <c r="F76" s="3">
         <v>30500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>29200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>28700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>27800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>27900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>26700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>26100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>25900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>17200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>16900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>18500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>21900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>19800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>19800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>19700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>19400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>19000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>20700</v>
-      </c>
-      <c r="W76" s="3">
-        <v>20800</v>
-      </c>
-      <c r="X76" s="3">
-        <v>21000</v>
       </c>
       <c r="Y76" s="3">
         <v>20800</v>
       </c>
       <c r="Z76" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>20800</v>
+      </c>
+      <c r="AB76" s="3">
         <v>20500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>19600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>22100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>22000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>22000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>22100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
       <c r="AD81" s="3">
         <v>0</v>
       </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6832,25 +7229,25 @@
         <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
       </c>
       <c r="M83" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
       </c>
       <c r="O83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
-        <v>600</v>
-      </c>
       <c r="Q83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>600</v>
@@ -6862,7 +7259,7 @@
         <v>600</v>
       </c>
       <c r="U83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V83" s="3">
         <v>600</v>
@@ -6871,16 +7268,16 @@
         <v>500</v>
       </c>
       <c r="X83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y83" s="3">
         <v>500</v>
       </c>
       <c r="Z83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AA83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB83" s="3">
         <v>600</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>4400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,22 +7922,24 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-700</v>
       </c>
       <c r="H91" s="3">
         <v>-500</v>
@@ -7510,58 +7951,58 @@
         <v>-500</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="L91" s="3">
         <v>-500</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O91" s="3">
         <v>-700</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-400</v>
       </c>
       <c r="X91" s="3">
         <v>-400</v>
       </c>
       <c r="Y91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-200</v>
       </c>
       <c r="AC91" s="3">
         <v>-200</v>
@@ -7570,13 +8011,19 @@
         <v>-200</v>
       </c>
       <c r="AE91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,22 +8212,28 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-700</v>
       </c>
       <c r="H94" s="3">
         <v>-500</v>
@@ -7786,73 +8245,79 @@
         <v>-500</v>
       </c>
       <c r="K94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>5800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-400</v>
       </c>
       <c r="X94" s="3">
         <v>-400</v>
       </c>
       <c r="Y94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Z94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AA94" s="3">
         <v>-300</v>
       </c>
       <c r="AB94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>3700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>1400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8359,44 +8856,44 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -8414,14 +8911,14 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -8431,102 +8928,114 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF101" s="3" t="s">
+      <c r="AH101" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E8" s="3">
         <v>34200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>36100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>52300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>23800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>26400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>28300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>30100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>29000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E9" s="3">
         <v>28800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>24700</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>23400</v>
       </c>
       <c r="AC9" s="3">
         <v>23400</v>
       </c>
       <c r="AD9" s="3">
+        <v>23400</v>
+      </c>
+      <c r="AE9" s="3">
         <v>24800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>26800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>25200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>25500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E10" s="3">
         <v>5400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>5500</v>
       </c>
       <c r="H10" s="3">
         <v>5500</v>
       </c>
       <c r="I10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J10" s="3">
         <v>5100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1149,25 +1163,25 @@
         <v>300</v>
       </c>
       <c r="J12" s="3">
+        <v>300</v>
+      </c>
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
       </c>
       <c r="N12" s="3">
         <v>100</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>200</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,13 +1338,16 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1341,8 +1361,8 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1354,25 +1374,25 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-6200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1389,8 +1409,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1398,20 +1418,20 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>200</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E17" s="3">
         <v>33100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>33300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>30000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>27800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>27300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>28000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>30200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>28200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>28700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1100</v>
       </c>
       <c r="H18" s="3">
         <v>1100</v>
       </c>
       <c r="I18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J18" s="3">
         <v>700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>800</v>
       </c>
       <c r="V18" s="3">
         <v>800</v>
       </c>
       <c r="W18" s="3">
+        <v>800</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3">
         <v>700</v>
       </c>
       <c r="AB18" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1827,13 +1861,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1880,19 +1914,22 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1600</v>
       </c>
       <c r="G21" s="3">
         <v>1600</v>
@@ -1901,85 +1938,88 @@
         <v>1600</v>
       </c>
       <c r="I21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J21" s="3">
         <v>1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
-      </c>
-      <c r="X21" s="3">
-        <v>500</v>
       </c>
       <c r="Y21" s="3">
         <v>500</v>
       </c>
       <c r="Z21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1987,7 +2027,7 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -2017,25 +2057,25 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
       </c>
       <c r="U22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>300</v>
@@ -2044,7 +2084,7 @@
         <v>300</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -2065,7 +2105,7 @@
         <v>200</v>
       </c>
       <c r="AE22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF22" s="3">
         <v>100</v>
@@ -2076,177 +2116,183 @@
       <c r="AH22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1000</v>
       </c>
       <c r="G23" s="3">
         <v>1000</v>
       </c>
       <c r="H23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>500</v>
       </c>
       <c r="AA23" s="3">
         <v>500</v>
       </c>
       <c r="AB23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
@@ -2255,25 +2301,28 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,92 +2419,95 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>400</v>
       </c>
       <c r="AA26" s="3">
         <v>400</v>
       </c>
       <c r="AB26" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
         <v>0</v>
       </c>
@@ -2463,97 +2515,100 @@
         <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>400</v>
       </c>
       <c r="AA27" s="3">
         <v>400</v>
       </c>
       <c r="AB27" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
         <v>0</v>
       </c>
@@ -2561,13 +2616,16 @@
         <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,17 +2787,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3003,13 +3073,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -3056,92 +3126,95 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>400</v>
       </c>
       <c r="AA33" s="3">
         <v>400</v>
       </c>
       <c r="AB33" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
         <v>0</v>
       </c>
@@ -3149,13 +3222,16 @@
         <v>0</v>
       </c>
       <c r="AG33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,92 +3328,95 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>400</v>
       </c>
       <c r="AA35" s="3">
         <v>400</v>
       </c>
       <c r="AB35" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
         <v>0</v>
       </c>
@@ -3345,116 +3424,122 @@
         <v>0</v>
       </c>
       <c r="AG35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,85 +3611,86 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>700</v>
-      </c>
-      <c r="P41" s="3">
-        <v>400</v>
       </c>
       <c r="Q41" s="3">
         <v>400</v>
       </c>
       <c r="R41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S41" s="3">
         <v>300</v>
       </c>
       <c r="T41" s="3">
+        <v>300</v>
+      </c>
+      <c r="U41" s="3">
         <v>700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>400</v>
       </c>
       <c r="AA41" s="3">
         <v>400</v>
       </c>
       <c r="AB41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC41" s="3">
         <v>500</v>
@@ -3612,19 +3699,22 @@
         <v>500</v>
       </c>
       <c r="AE41" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AF41" s="3">
         <v>200</v>
       </c>
       <c r="AG41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E43" s="3">
         <v>30200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>25600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>24300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>18600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>17500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E44" s="3">
         <v>23000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>22400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>21200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>20600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>17100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>15500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>15400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>14300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>16000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>15200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>14000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>21100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>21600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>21700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>20700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>2400</v>
       </c>
       <c r="P45" s="3">
         <v>2400</v>
       </c>
       <c r="Q45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R45" s="3">
         <v>5200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>2400</v>
       </c>
       <c r="U45" s="3">
         <v>2400</v>
       </c>
       <c r="V45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W45" s="3">
         <v>3800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E46" s="3">
         <v>59100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>54900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>58100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>56500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>52800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>51800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>51100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>46200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>40400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>40800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>43600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>45500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>43300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>48300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>46800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>50500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>45900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>43300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>39100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>37800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>41800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>40700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>40300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>39500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,79 +4316,82 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>14600</v>
       </c>
       <c r="L48" s="3">
         <v>14600</v>
       </c>
       <c r="M48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="N48" s="3">
         <v>14800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>14700</v>
       </c>
       <c r="W48" s="3">
         <v>14700</v>
       </c>
       <c r="X48" s="3">
+        <v>14700</v>
+      </c>
+      <c r="Y48" s="3">
         <v>15300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10200</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>10100</v>
       </c>
       <c r="AA48" s="3">
         <v>10100</v>
@@ -4292,25 +4400,28 @@
         <v>10100</v>
       </c>
       <c r="AC48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AD48" s="3">
         <v>10200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>10300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4318,7 +4429,7 @@
         <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F49" s="3">
         <v>300</v>
@@ -4327,7 +4438,7 @@
         <v>300</v>
       </c>
       <c r="H49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I49" s="3">
         <v>400</v>
@@ -4336,7 +4447,7 @@
         <v>400</v>
       </c>
       <c r="K49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L49" s="3">
         <v>500</v>
@@ -4348,28 +4459,28 @@
         <v>500</v>
       </c>
       <c r="O49" s="3">
+        <v>500</v>
+      </c>
+      <c r="P49" s="3">
         <v>1100</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1200</v>
       </c>
       <c r="Q49" s="3">
         <v>1200</v>
       </c>
       <c r="R49" s="3">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="S49" s="3">
         <v>3600</v>
       </c>
       <c r="T49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="U49" s="3">
         <v>3700</v>
       </c>
       <c r="V49" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="W49" s="3">
         <v>3800</v>
@@ -4378,37 +4489,40 @@
         <v>3800</v>
       </c>
       <c r="Y49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3900</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>4000</v>
       </c>
       <c r="AA49" s="3">
         <v>4000</v>
       </c>
       <c r="AB49" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="AC49" s="3">
         <v>4100</v>
       </c>
       <c r="AD49" s="3">
-        <v>5100</v>
+        <v>4100</v>
       </c>
       <c r="AE49" s="3">
         <v>5100</v>
       </c>
       <c r="AF49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AG49" s="3">
         <v>5200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4614,8 +4734,8 @@
       <c r="E52" s="3">
         <v>2600</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
+      <c r="F52" s="3">
+        <v>2600</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
@@ -4629,8 +4749,8 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4638,17 +4758,17 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
+      <c r="Q52" s="3">
+        <v>400</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
@@ -4659,8 +4779,8 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4687,10 +4807,10 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>500</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>600</v>
       </c>
       <c r="AF52" s="3">
         <v>600</v>
@@ -4699,10 +4819,13 @@
         <v>600</v>
       </c>
       <c r="AH52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E54" s="3">
         <v>75500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>66000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>73100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>67900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>67100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>62800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>60000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>61100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>63100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>61400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>65300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>69700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>55900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>52100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,114 +5099,118 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E57" s="3">
         <v>15200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>11200</v>
       </c>
       <c r="R57" s="3">
         <v>11200</v>
       </c>
       <c r="S57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="T57" s="3">
         <v>13500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>18100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>16900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14800</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>15300</v>
       </c>
       <c r="AF57" s="3">
         <v>15300</v>
       </c>
       <c r="AG57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AH57" s="3">
         <v>13800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
@@ -5097,25 +5231,25 @@
         <v>400</v>
       </c>
       <c r="L58" s="3">
+        <v>400</v>
+      </c>
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1900</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1100</v>
       </c>
       <c r="S58" s="3">
         <v>1100</v>
@@ -5124,40 +5258,40 @@
         <v>1100</v>
       </c>
       <c r="U58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V58" s="3">
         <v>1000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1300</v>
       </c>
       <c r="AC58" s="3">
         <v>1300</v>
       </c>
       <c r="AD58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE58" s="3">
         <v>1200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1600</v>
       </c>
       <c r="AG58" s="3">
         <v>1600</v>
@@ -5165,88 +5299,91 @@
       <c r="AH58" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E59" s="3">
         <v>10200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5100</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>5000</v>
       </c>
       <c r="AD59" s="3">
         <v>5000</v>
@@ -5255,220 +5392,229 @@
         <v>5000</v>
       </c>
       <c r="AF59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG59" s="3">
         <v>3900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E60" s="3">
         <v>25700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>23800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>22200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>28100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>18400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>21400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>20800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>20300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10600</v>
-      </c>
-      <c r="S61" s="3">
-        <v>14900</v>
       </c>
       <c r="T61" s="3">
         <v>14900</v>
       </c>
       <c r="U61" s="3">
+        <v>14900</v>
+      </c>
+      <c r="V61" s="3">
         <v>14700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E62" s="3">
         <v>7400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>7200</v>
       </c>
       <c r="F62" s="3">
         <v>7200</v>
@@ -5477,88 +5623,91 @@
         <v>7200</v>
       </c>
       <c r="H62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I62" s="3">
         <v>7400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9500</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>9000</v>
       </c>
       <c r="R62" s="3">
         <v>9000</v>
       </c>
       <c r="S62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="T62" s="3">
         <v>4200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>200</v>
       </c>
       <c r="AA62" s="3">
         <v>200</v>
       </c>
       <c r="AB62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC62" s="3">
         <v>100</v>
       </c>
       <c r="AD62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE62" s="3">
         <v>400</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>600</v>
       </c>
       <c r="AF62" s="3">
         <v>600</v>
       </c>
       <c r="AG62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH62" s="3">
         <v>700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E66" s="3">
         <v>39400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>41100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>43000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>46100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>36100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,91 +6548,94 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E72" s="3">
         <v>19400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>6300</v>
       </c>
       <c r="AE72" s="3">
         <v>6300</v>
@@ -6473,10 +6647,13 @@
         <v>6300</v>
       </c>
       <c r="AH72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AI72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E76" s="3">
         <v>35800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>30500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21900</v>
-      </c>
-      <c r="S76" s="3">
-        <v>19800</v>
       </c>
       <c r="T76" s="3">
         <v>19800</v>
       </c>
       <c r="U76" s="3">
+        <v>19800</v>
+      </c>
+      <c r="V76" s="3">
         <v>19700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22100</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>22000</v>
       </c>
       <c r="AF76" s="3">
         <v>22000</v>
       </c>
       <c r="AG76" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AH76" s="3">
         <v>22100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,195 +7154,201 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>400</v>
       </c>
       <c r="AA81" s="3">
         <v>400</v>
       </c>
       <c r="AB81" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
         <v>0</v>
       </c>
@@ -7161,13 +7356,16 @@
         <v>0</v>
       </c>
       <c r="AG81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7235,22 +7434,22 @@
         <v>500</v>
       </c>
       <c r="M83" s="3">
+        <v>500</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>500</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
       </c>
       <c r="R83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S83" s="3">
         <v>600</v>
@@ -7265,13 +7464,13 @@
         <v>600</v>
       </c>
       <c r="W83" s="3">
+        <v>600</v>
+      </c>
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>600</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>500</v>
       </c>
       <c r="Z83" s="3">
         <v>500</v>
@@ -7280,7 +7479,7 @@
         <v>500</v>
       </c>
       <c r="AB83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AC83" s="3">
         <v>600</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,73 +8144,74 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-500</v>
       </c>
       <c r="I91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-200</v>
       </c>
       <c r="S91" s="3">
         <v>-200</v>
       </c>
       <c r="T91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-400</v>
       </c>
       <c r="Y91" s="3">
         <v>-400</v>
@@ -7999,13 +8220,13 @@
         <v>-400</v>
       </c>
       <c r="AA91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AB91" s="3">
         <v>-300</v>
       </c>
       <c r="AC91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AD91" s="3">
         <v>-200</v>
@@ -8017,13 +8238,16 @@
         <v>-200</v>
       </c>
       <c r="AG91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AH91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,73 +8445,76 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-200</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
       </c>
       <c r="G94" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="H94" s="3">
         <v>-500</v>
       </c>
       <c r="I94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-400</v>
       </c>
       <c r="Y94" s="3">
         <v>-400</v>
@@ -8293,7 +8523,7 @@
         <v>-400</v>
       </c>
       <c r="AA94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AB94" s="3">
         <v>-300</v>
@@ -8302,22 +8532,25 @@
         <v>-300</v>
       </c>
       <c r="AD94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE94" s="3">
         <v>-200</v>
       </c>
       <c r="AF94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG94" s="3">
         <v>400</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-300</v>
       </c>
       <c r="AH94" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-100</v>
       </c>
       <c r="T100" s="3">
         <v>-100</v>
       </c>
       <c r="U100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V100" s="3">
         <v>-2600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-300</v>
       </c>
       <c r="AC100" s="3">
         <v>-300</v>
       </c>
       <c r="AD100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8862,8 +9111,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
@@ -8871,11 +9120,11 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
@@ -8883,11 +9132,11 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
@@ -8895,8 +9144,8 @@
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -8917,11 +9166,11 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -8934,108 +9183,114 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>8</v>
+      <c r="AG101" s="3">
+        <v>0</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>NSYS</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E8" s="3">
         <v>33900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>36100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>52300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>27400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>25600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>28300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>30100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>28300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>29000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E9" s="3">
         <v>29300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>29400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>24700</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>23400</v>
       </c>
       <c r="AD9" s="3">
         <v>23400</v>
       </c>
       <c r="AE9" s="3">
+        <v>23400</v>
+      </c>
+      <c r="AF9" s="3">
         <v>24800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>26800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>25200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>25500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E10" s="3">
         <v>4600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5400</v>
       </c>
-      <c r="F10" s="3">
-        <v>6900</v>
-      </c>
       <c r="G10" s="3">
-        <v>5400</v>
+        <v>6800</v>
       </c>
       <c r="H10" s="3">
-        <v>5500</v>
+        <v>5300</v>
       </c>
       <c r="I10" s="3">
         <v>5500</v>
       </c>
       <c r="J10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K10" s="3">
         <v>5100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,26 +1180,26 @@
         <v>300</v>
       </c>
       <c r="K12" s="3">
+        <v>300</v>
+      </c>
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
       <c r="P12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,17 +1358,20 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1364,8 +1384,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1377,25 +1397,25 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-6200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2400</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1412,8 +1432,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1421,52 +1441,55 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>200</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,123 +1603,127 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E17" s="3">
         <v>33500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>33300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>30000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>29300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>27800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>26600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>27300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>28000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>30200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>28200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>28700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
-        <v>1100</v>
-      </c>
       <c r="F18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G18" s="3">
         <v>2700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1200</v>
       </c>
       <c r="H18" s="3">
         <v>1100</v>
@@ -1702,85 +1732,88 @@
         <v>1100</v>
       </c>
       <c r="J18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K18" s="3">
         <v>700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>800</v>
       </c>
       <c r="W18" s="3">
         <v>800</v>
       </c>
       <c r="X18" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="3">
         <v>700</v>
       </c>
       <c r="AC18" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,31 +1849,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1864,13 +1898,13 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1917,22 +1951,25 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
+        <v>900</v>
+      </c>
+      <c r="F21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1600</v>
       </c>
       <c r="H21" s="3">
         <v>1600</v>
@@ -1941,85 +1978,88 @@
         <v>1600</v>
       </c>
       <c r="J21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>500</v>
       </c>
       <c r="Z21" s="3">
         <v>500</v>
       </c>
       <c r="AA21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB21" s="3">
         <v>1200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2030,7 +2070,7 @@
         <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -2060,25 +2100,25 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
       </c>
       <c r="V22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>300</v>
@@ -2087,7 +2127,7 @@
         <v>300</v>
       </c>
       <c r="Y22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
@@ -2108,7 +2148,7 @@
         <v>200</v>
       </c>
       <c r="AF22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG22" s="3">
         <v>100</v>
@@ -2119,183 +2159,189 @@
       <c r="AI22" s="3">
         <v>100</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1000</v>
       </c>
       <c r="H23" s="3">
         <v>1000</v>
       </c>
       <c r="I23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>500</v>
       </c>
       <c r="AB23" s="3">
         <v>500</v>
       </c>
       <c r="AC23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
@@ -2304,25 +2350,28 @@
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,95 +2471,98 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>400</v>
       </c>
       <c r="AB26" s="3">
         <v>400</v>
       </c>
       <c r="AC26" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
         <v>0</v>
       </c>
@@ -2518,100 +2570,103 @@
         <v>0</v>
       </c>
       <c r="AH26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3">
         <v>100</v>
       </c>
+      <c r="AJ26" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>400</v>
       </c>
       <c r="AB27" s="3">
         <v>400</v>
       </c>
       <c r="AC27" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
         <v>0</v>
       </c>
@@ -2619,13 +2674,16 @@
         <v>0</v>
       </c>
       <c r="AH27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3">
         <v>100</v>
       </c>
+      <c r="AJ27" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,17 +2851,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2808,12 +2869,12 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-300</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,31 +3095,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3076,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -3129,95 +3199,98 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>400</v>
       </c>
       <c r="AB33" s="3">
         <v>400</v>
       </c>
       <c r="AC33" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
         <v>0</v>
       </c>
@@ -3225,13 +3298,16 @@
         <v>0</v>
       </c>
       <c r="AH33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3">
         <v>100</v>
       </c>
+      <c r="AJ33" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,95 +3407,98 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>400</v>
       </c>
       <c r="AB35" s="3">
         <v>400</v>
       </c>
       <c r="AC35" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
         <v>0</v>
       </c>
@@ -3427,119 +3506,125 @@
         <v>0</v>
       </c>
       <c r="AH35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3">
         <v>100</v>
       </c>
+      <c r="AJ35" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,88 +3698,89 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>400</v>
       </c>
       <c r="R41" s="3">
         <v>400</v>
       </c>
       <c r="S41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T41" s="3">
         <v>300</v>
       </c>
       <c r="U41" s="3">
+        <v>300</v>
+      </c>
+      <c r="V41" s="3">
         <v>700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>400</v>
       </c>
       <c r="AB41" s="3">
         <v>400</v>
       </c>
       <c r="AC41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD41" s="3">
         <v>500</v>
@@ -3702,19 +3789,22 @@
         <v>500</v>
       </c>
       <c r="AF41" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AG41" s="3">
         <v>200</v>
       </c>
       <c r="AH41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI41" s="3">
         <v>300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,435 +3904,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E43" s="3">
         <v>32500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>33800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>24300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>17600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>18600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>17500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E44" s="3">
         <v>22800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>23000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>21200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>20600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>18300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>17100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>14500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>15500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>15400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>14300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>16300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>16000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>17000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>15200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>14000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>21100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>21600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>21700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>20700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2400</v>
       </c>
       <c r="Q45" s="3">
         <v>2400</v>
       </c>
       <c r="R45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S45" s="3">
         <v>5200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>2400</v>
       </c>
       <c r="V45" s="3">
         <v>2400</v>
       </c>
       <c r="W45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X45" s="3">
         <v>3800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E46" s="3">
         <v>59200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>58800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>54400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>54900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>58100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>56500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>52800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>51800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>51100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>46200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>40400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>43600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>43300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>48300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>46800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>50500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>45900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>43300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>41800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>39100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>37800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>40700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>40300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>39500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,82 +4424,85 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E48" s="3">
         <v>14300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>14600</v>
       </c>
       <c r="M48" s="3">
         <v>14600</v>
       </c>
       <c r="N48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="O48" s="3">
         <v>14800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14400</v>
-      </c>
-      <c r="W48" s="3">
-        <v>14700</v>
       </c>
       <c r="X48" s="3">
         <v>14700</v>
       </c>
       <c r="Y48" s="3">
+        <v>14700</v>
+      </c>
+      <c r="Z48" s="3">
         <v>15300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10200</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>10100</v>
       </c>
       <c r="AB48" s="3">
         <v>10100</v>
@@ -4403,25 +4511,28 @@
         <v>10100</v>
       </c>
       <c r="AD48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AE48" s="3">
         <v>10200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4432,7 +4543,7 @@
         <v>200</v>
       </c>
       <c r="F49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
@@ -4441,7 +4552,7 @@
         <v>300</v>
       </c>
       <c r="I49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J49" s="3">
         <v>400</v>
@@ -4450,7 +4561,7 @@
         <v>400</v>
       </c>
       <c r="L49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M49" s="3">
         <v>500</v>
@@ -4462,28 +4573,28 @@
         <v>500</v>
       </c>
       <c r="P49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1200</v>
       </c>
       <c r="R49" s="3">
         <v>1200</v>
       </c>
       <c r="S49" s="3">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="T49" s="3">
         <v>3600</v>
       </c>
       <c r="U49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="V49" s="3">
         <v>3700</v>
       </c>
       <c r="W49" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="X49" s="3">
         <v>3800</v>
@@ -4492,37 +4603,40 @@
         <v>3800</v>
       </c>
       <c r="Z49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA49" s="3">
         <v>3900</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>4000</v>
       </c>
       <c r="AB49" s="3">
         <v>4000</v>
       </c>
       <c r="AC49" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="AD49" s="3">
         <v>4100</v>
       </c>
       <c r="AE49" s="3">
-        <v>5100</v>
+        <v>4100</v>
       </c>
       <c r="AF49" s="3">
         <v>5100</v>
       </c>
       <c r="AG49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AH49" s="3">
         <v>5200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,19 +4840,22 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>2600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2600</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
@@ -4752,8 +4872,8 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4761,17 +4881,17 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P52" s="3">
-        <v>400</v>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
+      <c r="R52" s="3">
+        <v>400</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
@@ -4782,8 +4902,8 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4810,10 +4930,10 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
         <v>500</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>600</v>
       </c>
       <c r="AG52" s="3">
         <v>600</v>
@@ -4822,10 +4942,13 @@
         <v>600</v>
       </c>
       <c r="AI52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E54" s="3">
         <v>76300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>75100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>68400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>67900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>60000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>61100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>63100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>61400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>65300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>69700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>60000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>55900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>53300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,132 +5230,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E57" s="3">
         <v>12700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>11200</v>
       </c>
       <c r="S57" s="3">
         <v>11200</v>
       </c>
       <c r="T57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="U57" s="3">
         <v>13500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>16800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14800</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>15300</v>
       </c>
       <c r="AG57" s="3">
         <v>15300</v>
       </c>
       <c r="AH57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AI57" s="3">
         <v>13800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="G58" s="3">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="H58" s="3">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="J58" s="3">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>400</v>
@@ -5234,25 +5368,25 @@
         <v>400</v>
       </c>
       <c r="M58" s="3">
+        <v>400</v>
+      </c>
+      <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1900</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1100</v>
       </c>
       <c r="T58" s="3">
         <v>1100</v>
@@ -5261,40 +5395,40 @@
         <v>1100</v>
       </c>
       <c r="V58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W58" s="3">
         <v>1000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1400</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>1300</v>
       </c>
       <c r="AD58" s="3">
         <v>1300</v>
       </c>
       <c r="AE58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AF58" s="3">
         <v>1200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>1600</v>
       </c>
       <c r="AH58" s="3">
         <v>1600</v>
@@ -5302,91 +5436,94 @@
       <c r="AI58" s="3">
         <v>1600</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10400</v>
+        <v>5300</v>
       </c>
       <c r="E59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K59" s="3">
+        <v>11200</v>
+      </c>
+      <c r="L59" s="3">
+        <v>11500</v>
+      </c>
+      <c r="M59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N59" s="3">
         <v>10200</v>
       </c>
-      <c r="F59" s="3">
-        <v>10300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>9700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>8700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>14000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>11200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>11500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>10200</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5100</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>5000</v>
       </c>
       <c r="AE59" s="3">
         <v>5000</v>
@@ -5395,16 +5532,19 @@
         <v>5000</v>
       </c>
       <c r="AG59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AH59" s="3">
         <v>3900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5412,302 +5552,311 @@
         <v>23300</v>
       </c>
       <c r="E60" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F60" s="3">
         <v>25700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>22200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>23100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>22700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>18000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>21400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>20800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>20300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8500</v>
+        <v>17500</v>
       </c>
       <c r="E61" s="3">
-        <v>6300</v>
+        <v>16400</v>
       </c>
       <c r="F61" s="3">
-        <v>6000</v>
+        <v>13300</v>
       </c>
       <c r="G61" s="3">
-        <v>4900</v>
+        <v>12800</v>
       </c>
       <c r="H61" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I61" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J61" s="3">
+        <v>13600</v>
+      </c>
+      <c r="K61" s="3">
         <v>7400</v>
       </c>
-      <c r="I61" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>7400</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10600</v>
-      </c>
-      <c r="T61" s="3">
-        <v>14900</v>
       </c>
       <c r="U61" s="3">
         <v>14900</v>
       </c>
       <c r="V61" s="3">
+        <v>14900</v>
+      </c>
+      <c r="W61" s="3">
         <v>14700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>12100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8400</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>7400</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>7200</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>7200</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>7200</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>7400</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
         <v>7600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9500</v>
-      </c>
-      <c r="R62" s="3">
-        <v>9000</v>
       </c>
       <c r="S62" s="3">
         <v>9000</v>
       </c>
       <c r="T62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="U62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>100</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>200</v>
       </c>
       <c r="AB62" s="3">
         <v>200</v>
       </c>
       <c r="AC62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD62" s="3">
         <v>100</v>
       </c>
       <c r="AE62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF62" s="3">
         <v>400</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>600</v>
       </c>
       <c r="AG62" s="3">
         <v>600</v>
       </c>
       <c r="AH62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI62" s="3">
         <v>700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E66" s="3">
         <v>40100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>41500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>44600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>41100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>41400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>47100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>46100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>36100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>35200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>300</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,94 +6722,97 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E72" s="3">
         <v>19600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>6300</v>
       </c>
       <c r="AF72" s="3">
         <v>6300</v>
@@ -6650,10 +6824,13 @@
         <v>6300</v>
       </c>
       <c r="AI72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E76" s="3">
         <v>35900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21900</v>
-      </c>
-      <c r="T76" s="3">
-        <v>19800</v>
       </c>
       <c r="U76" s="3">
         <v>19800</v>
       </c>
       <c r="V76" s="3">
+        <v>19800</v>
+      </c>
+      <c r="W76" s="3">
         <v>19700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22100</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>22000</v>
       </c>
       <c r="AG76" s="3">
         <v>22000</v>
       </c>
       <c r="AH76" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AI76" s="3">
         <v>22100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,201 +7346,207 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>400</v>
       </c>
       <c r="AB81" s="3">
         <v>400</v>
       </c>
       <c r="AC81" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
         <v>0</v>
       </c>
@@ -7359,13 +7554,16 @@
         <v>0</v>
       </c>
       <c r="AH81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI81" s="3">
         <v>100</v>
       </c>
+      <c r="AJ81" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7416,13 +7615,13 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
@@ -7437,22 +7636,22 @@
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>500</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T83" s="3">
         <v>600</v>
@@ -7467,13 +7666,13 @@
         <v>600</v>
       </c>
       <c r="X83" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y83" s="3">
         <v>500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>600</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>500</v>
       </c>
       <c r="AA83" s="3">
         <v>500</v>
@@ -7482,7 +7681,7 @@
         <v>500</v>
       </c>
       <c r="AC83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD83" s="3">
         <v>600</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>600</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>600</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,76 +8365,77 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>-500</v>
       </c>
       <c r="J91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-200</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
       <c r="U91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-400</v>
       </c>
       <c r="Z91" s="3">
         <v>-400</v>
@@ -8223,13 +8444,13 @@
         <v>-400</v>
       </c>
       <c r="AB91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AC91" s="3">
         <v>-300</v>
       </c>
       <c r="AD91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE91" s="3">
         <v>-200</v>
@@ -8241,13 +8462,16 @@
         <v>-200</v>
       </c>
       <c r="AH91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AI91" s="3">
         <v>-300</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,76 +8675,79 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-200</v>
       </c>
       <c r="G94" s="3">
         <v>-200</v>
       </c>
       <c r="H94" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="I94" s="3">
         <v>-500</v>
       </c>
       <c r="J94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-400</v>
       </c>
       <c r="Z94" s="3">
         <v>-400</v>
@@ -8526,7 +8756,7 @@
         <v>-400</v>
       </c>
       <c r="AB94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AC94" s="3">
         <v>-300</v>
@@ -8535,22 +8765,25 @@
         <v>-300</v>
       </c>
       <c r="AE94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AF94" s="3">
         <v>-200</v>
       </c>
       <c r="AG94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH94" s="3">
         <v>400</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-300</v>
       </c>
       <c r="AI94" s="3">
         <v>-300</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,109 +9233,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-100</v>
       </c>
       <c r="U100" s="3">
         <v>-100</v>
       </c>
       <c r="V100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W100" s="3">
         <v>-2600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-300</v>
       </c>
       <c r="AD100" s="3">
         <v>-300</v>
       </c>
       <c r="AE100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9106,13 +9355,13 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
@@ -9123,11 +9372,11 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
@@ -9135,11 +9384,11 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
@@ -9147,8 +9396,8 @@
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -9169,11 +9418,11 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -9186,111 +9435,117 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>8</v>
+      <c r="AH101" s="3">
+        <v>0</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>NSYS</t>
   </si>
@@ -656,467 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F8" s="3">
         <v>31400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>33900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>34200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>36100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>33400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>35000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>34900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>35600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>35300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>32500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>30700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>33500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>29500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>52300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>22100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>23800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>26400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>26500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>27400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>30800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>30100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>27300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>28200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>28800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>29600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>28500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>26400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>25600</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>28300</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>30100</v>
       </c>
       <c r="AH8" s="3">
         <v>28300</v>
       </c>
       <c r="AI8" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AK8" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F9" s="3">
         <v>27600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>29300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>28800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>29200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>28100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>29500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>29400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>30500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>28900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>27500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>26700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>30800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>21400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>47100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>20500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>22100</v>
-      </c>
-      <c r="T9" s="3">
-        <v>24400</v>
-      </c>
-      <c r="U9" s="3">
-        <v>24000</v>
       </c>
       <c r="V9" s="3">
         <v>24400</v>
       </c>
       <c r="W9" s="3">
+        <v>24000</v>
+      </c>
+      <c r="X9" s="3">
+        <v>24400</v>
+      </c>
+      <c r="Y9" s="3">
         <v>27200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>26400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>25000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>25200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>25700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>26200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>24700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>23400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>23400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>24800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>26800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>25200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>25500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F10" s="3">
         <v>3800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>5300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>6400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>8100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>3100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>3300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>3100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1178,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1183,29 +1210,29 @@
         <v>300</v>
       </c>
       <c r="L12" s="3">
+        <v>300</v>
+      </c>
+      <c r="M12" s="3">
+        <v>300</v>
+      </c>
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1284,14 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,23 +1394,29 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1387,11 +1426,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1400,28 +1439,28 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-6200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>2400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1435,49 +1474,55 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>200</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
@@ -1492,10 +1537,10 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1569,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F17" s="3">
         <v>31700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>33500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>33100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>33400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>32200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>33900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>33800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>34900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>33300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>31500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>30500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>28200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>24500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>54000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>24200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>27600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>23700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>26400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>27000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>30000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>29300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>28500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>28300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>28800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>28900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>27800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>26600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>27300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>28000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>30200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>28200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>28700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>2700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1100</v>
       </c>
       <c r="J18" s="3">
         <v>1100</v>
       </c>
       <c r="K18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M18" s="3">
         <v>700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1915,10 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,11 +1943,11 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1901,17 +1968,17 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1954,112 +2021,124 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>3200</v>
       </c>
       <c r="H21" s="3">
         <v>1600</v>
       </c>
       <c r="I21" s="3">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="J21" s="3">
         <v>1600</v>
       </c>
       <c r="K21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M21" s="3">
         <v>1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>5500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2073,10 +2152,10 @@
         <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -2103,7 +2182,7 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
@@ -2112,28 +2191,28 @@
         <v>200</v>
       </c>
       <c r="T22" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
       </c>
       <c r="V22" s="3">
+        <v>300</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
-        <v>300</v>
-      </c>
       <c r="X22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>300</v>
       </c>
       <c r="Z22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB22" s="3">
         <v>200</v>
@@ -2151,10 +2230,10 @@
         <v>200</v>
       </c>
       <c r="AG22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI22" s="3">
         <v>100</v>
@@ -2162,216 +2241,234 @@
       <c r="AJ22" s="3">
         <v>100</v>
       </c>
+      <c r="AK22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2600</v>
       </c>
       <c r="H23" s="3">
         <v>1000</v>
       </c>
       <c r="I23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>4800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1100</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="N24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>200</v>
+      </c>
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>100</v>
       </c>
       <c r="AE24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>100</v>
       </c>
       <c r="AG24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>4400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>0</v>
-      </c>
       <c r="AH26" s="3">
         <v>0</v>
       </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>4400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
         <v>0</v>
       </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,33 +2975,33 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-300</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3231,14 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,11 +3263,11 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3149,17 +3288,17 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3202,112 +3341,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>4400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
         <v>0</v>
       </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>4400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
         <v>0</v>
       </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,8 +3870,10 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3708,103 +3881,109 @@
         <v>1200</v>
       </c>
       <c r="E41" s="3">
+        <v>900</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
-      </c>
-      <c r="J41" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1000</v>
       </c>
       <c r="L41" s="3">
         <v>1300</v>
       </c>
       <c r="M41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
-      </c>
-      <c r="P41" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>700</v>
       </c>
       <c r="R41" s="3">
         <v>400</v>
       </c>
       <c r="S41" s="3">
+        <v>700</v>
+      </c>
+      <c r="T41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
+        <v>400</v>
+      </c>
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
-      </c>
-      <c r="W41" s="3">
-        <v>400</v>
-      </c>
-      <c r="X41" s="3">
-        <v>200</v>
       </c>
       <c r="Y41" s="3">
         <v>400</v>
       </c>
       <c r="Z41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>400</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>500</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>500</v>
       </c>
       <c r="AF41" s="3">
         <v>500</v>
       </c>
       <c r="AG41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI41" s="3">
         <v>200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,221 +4086,239 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>28700</v>
+      </c>
+      <c r="F43" s="3">
         <v>31600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>32500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>30200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>33800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>28100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>29000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>29700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>28600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>30600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>30700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>28000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>28500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>27300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>24800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>20500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>21500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>23400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>25600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>27000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>26200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>27300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>27900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>31700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>26500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>26100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>25900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>24300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>17600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>18600</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>17500</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>17300</v>
       </c>
       <c r="AI43" s="3">
         <v>17500</v>
       </c>
       <c r="AJ43" s="3">
+        <v>17300</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="AL43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>21600</v>
+      </c>
+      <c r="F44" s="3">
         <v>22300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>22800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>23000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>21700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>21500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>21100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>21300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>22400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>23600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>23000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>21200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>19400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>20600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>18300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>17100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>13900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>14500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>15500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>15400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>14300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>16900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>16300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>16000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>17000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>15200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>14000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>13000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>18500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>21100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>21600</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>21700</v>
-      </c>
-      <c r="AI44" s="3">
-        <v>20700</v>
       </c>
       <c r="AJ44" s="3">
         <v>21700</v>
       </c>
+      <c r="AK44" s="3">
+        <v>20700</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>21700</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>500</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4141,190 +4338,202 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3200</v>
       </c>
       <c r="P45" s="3">
         <v>2800</v>
       </c>
       <c r="Q45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F46" s="3">
         <v>60300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>59200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>59100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>58800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>52600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>54400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>55600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>54900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>58100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>56500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>52800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>51800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>51100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>46200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>40400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>41000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>40800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>43600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>45500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>43300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>48300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>46800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>50500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>45900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>43300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>41800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>39100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>37800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>41800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>40700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>40300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>39500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,11 +4558,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4427,112 +4636,124 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F48" s="3">
         <v>13900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>14300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>13400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>14500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>14600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>14600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>14900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>15100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>15500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>15400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>15600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>13800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>14000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>14400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>14700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>14700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>15300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>10200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>10100</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>10100</v>
       </c>
       <c r="AD48" s="3">
         <v>10100</v>
       </c>
       <c r="AE48" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="AF48" s="3">
         <v>10100</v>
       </c>
       <c r="AG48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AI48" s="3">
         <v>9500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>9700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4546,28 +4767,28 @@
         <v>200</v>
       </c>
       <c r="G49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I49" s="3">
         <v>300</v>
       </c>
       <c r="J49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L49" s="3">
         <v>400</v>
       </c>
       <c r="M49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O49" s="3">
         <v>500</v>
@@ -4576,58 +4797,58 @@
         <v>500</v>
       </c>
       <c r="Q49" s="3">
+        <v>500</v>
+      </c>
+      <c r="R49" s="3">
+        <v>500</v>
+      </c>
+      <c r="S49" s="3">
         <v>1100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3700</v>
-      </c>
-      <c r="X49" s="3">
-        <v>3800</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>3800</v>
       </c>
       <c r="Z49" s="3">
         <v>3800</v>
       </c>
       <c r="AA49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AC49" s="3">
         <v>3900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>4000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>4000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>4100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>4100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>5100</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>5200</v>
       </c>
       <c r="AI49" s="3">
         <v>5100</v>
@@ -4635,8 +4856,14 @@
       <c r="AJ49" s="3">
         <v>5200</v>
       </c>
+      <c r="AK49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,13 +5076,19 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>100</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -4875,41 +5114,41 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4933,22 +5172,28 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>500</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>600</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>600</v>
       </c>
       <c r="AI52" s="3">
         <v>600</v>
       </c>
       <c r="AJ52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>72400</v>
+      </c>
+      <c r="F54" s="3">
         <v>77000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>76300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>75500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>75100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>66000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>68400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>70100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>69500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>73100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>71500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>67900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>67100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>66500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>62800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>57500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>57600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>60000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>61100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>63100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>61400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>66800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>65300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>69700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>60000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>57400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>55900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>53300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>52100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>57500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>55900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>55800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>55500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,112 +5490,120 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F57" s="3">
         <v>12300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>12700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>15900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>13100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>15300</v>
       </c>
       <c r="J57" s="3">
         <v>13100</v>
       </c>
       <c r="K57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="L57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="M57" s="3">
         <v>14800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>14700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>14100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>14000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>12700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>14100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>12800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>13000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>13500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>16400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>14000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>18400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>16800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>21100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>18100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>16900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>15700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>12100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>11700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>14800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>15300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>15300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5344,519 +5611,549 @@
         <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F58" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="G58" s="3">
         <v>1400</v>
       </c>
       <c r="H58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>400</v>
       </c>
       <c r="M58" s="3">
         <v>400</v>
       </c>
       <c r="N58" s="3">
+        <v>400</v>
+      </c>
+      <c r="O58" s="3">
+        <v>400</v>
+      </c>
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>9800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>11400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U58" s="3">
-        <v>1100</v>
       </c>
       <c r="V58" s="3">
         <v>1100</v>
       </c>
       <c r="W58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>900</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>1200</v>
       </c>
       <c r="Z58" s="3">
         <v>900</v>
       </c>
       <c r="AA58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>1600</v>
       </c>
       <c r="AJ58" s="3">
         <v>1600</v>
       </c>
+      <c r="AK58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F59" s="3">
         <v>5300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>11200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>9700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>10200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>9000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>8900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>7100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>6400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>7200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>6300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>6700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>6100</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>5600</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>5000</v>
       </c>
       <c r="AC59" s="3">
         <v>5600</v>
       </c>
       <c r="AD59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AF59" s="3">
         <v>5100</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>5000</v>
       </c>
       <c r="AG59" s="3">
         <v>5000</v>
       </c>
       <c r="AH59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>3900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F60" s="3">
         <v>23300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>23300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>25700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>26600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>23200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>24400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>27400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>26400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>26600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>24300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>24700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>22300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>32900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>31400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>22700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>19500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>18200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>21900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>23800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>22200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>25600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>24800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>28100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>24900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>23100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>22700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>18400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>18000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>20900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>21400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>20800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F61" s="3">
         <v>17500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>16400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>13300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>12800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>14500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>13600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>12100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>8400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>10300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>10600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>14900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>14900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>14700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>16900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>16500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>15700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>13800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>12800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>12100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>14000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>14100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>13900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>11500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>12000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>12200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
       <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>7900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>8200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>8500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>8800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>8900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>9300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>9500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>9000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>9000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>4500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>4600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>4800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>38400</v>
+      </c>
+      <c r="F66" s="3">
         <v>41300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>40100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>39400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>39800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>35300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>38900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>41500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>44900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>44600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>41600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>41000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>45500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>45400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>40300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>38900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>37800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>41100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>43000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>41400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>47100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>46100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>48700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>38900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>36100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>34900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>32500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>32300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>35200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>33600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>33500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>33200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>300</v>
       </c>
+      <c r="AK70" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,100 +7066,106 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F72" s="3">
         <v>18900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>19600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>19400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>18700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>14300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>13100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>12500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>11800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>12200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>10700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6200</v>
-      </c>
-      <c r="U72" s="3">
-        <v>4200</v>
-      </c>
-      <c r="V72" s="3">
-        <v>4300</v>
       </c>
       <c r="W72" s="3">
         <v>4200</v>
       </c>
       <c r="X72" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Y72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z72" s="3">
         <v>3900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>4900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AF72" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>6300</v>
       </c>
       <c r="AH72" s="3">
         <v>6300</v>
@@ -6827,10 +7174,16 @@
         <v>6300</v>
       </c>
       <c r="AJ72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AK72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AL72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>33800</v>
+      </c>
+      <c r="F76" s="3">
         <v>35400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>35900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>35800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>35100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>30500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>29200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>28700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>27800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>27900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>26700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>26100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>25900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>20800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>17200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>16900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>18500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>21900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>19800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>19800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>19700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>19400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>19000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>20700</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>20800</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>21000</v>
       </c>
       <c r="AC76" s="3">
         <v>20800</v>
       </c>
       <c r="AD76" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AE76" s="3">
+        <v>20800</v>
+      </c>
+      <c r="AF76" s="3">
         <v>20500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>19600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>22100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>22000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>22000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>4400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
         <v>0</v>
       </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,13 +7995,15 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
@@ -7615,19 +8012,19 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
@@ -7639,25 +8036,25 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
       </c>
       <c r="Q83" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T83" s="3">
         <v>500</v>
       </c>
-      <c r="T83" s="3">
-        <v>600</v>
-      </c>
       <c r="U83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="V83" s="3">
         <v>600</v>
@@ -7669,7 +8066,7 @@
         <v>600</v>
       </c>
       <c r="Y83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Z83" s="3">
         <v>600</v>
@@ -7678,16 +8075,16 @@
         <v>500</v>
       </c>
       <c r="AB83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AC83" s="3">
         <v>500</v>
       </c>
       <c r="AD83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AE83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AF83" s="3">
         <v>600</v>
@@ -7704,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>600</v>
       </c>
+      <c r="AK83" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>600</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,34 +8805,36 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
         <v>-300</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-700</v>
       </c>
       <c r="L91" s="3">
         <v>-500</v>
@@ -8405,58 +8846,58 @@
         <v>-500</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="P91" s="3">
         <v>-500</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S91" s="3">
         <v>-700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
       <c r="U91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-400</v>
       </c>
       <c r="AB91" s="3">
         <v>-400</v>
       </c>
       <c r="AC91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-200</v>
       </c>
       <c r="AG91" s="3">
         <v>-200</v>
@@ -8465,13 +8906,19 @@
         <v>-200</v>
       </c>
       <c r="AI91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,34 +9131,40 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
         <v>-300</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-700</v>
       </c>
       <c r="L94" s="3">
         <v>-500</v>
@@ -8717,73 +9176,79 @@
         <v>-500</v>
       </c>
       <c r="O94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>5800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-400</v>
       </c>
       <c r="AB94" s="3">
         <v>-400</v>
       </c>
       <c r="AC94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AD94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AE94" s="3">
         <v>-300</v>
       </c>
       <c r="AF94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9313,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9721,124 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>3800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-4300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-2600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>1600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>1400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9355,14 +9852,14 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
@@ -9375,35 +9872,35 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -9421,14 +9918,14 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9438,114 +9935,126 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ101" s="3" t="s">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL101" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>NSYS</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E8" s="3">
         <v>26900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>36100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>52300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>23800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>29600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>28500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>26400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>25600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>28300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>28300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>29000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E9" s="3">
         <v>23800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>29200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>22100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>27200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>25000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>25200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>26200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>24700</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>23400</v>
       </c>
       <c r="AG9" s="3">
         <v>23400</v>
       </c>
       <c r="AH9" s="3">
+        <v>23400</v>
+      </c>
+      <c r="AI9" s="3">
         <v>24800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>25200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>25500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E10" s="3">
         <v>3100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>5500</v>
       </c>
       <c r="L10" s="3">
         <v>5500</v>
       </c>
       <c r="M10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N10" s="3">
         <v>5100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1216,26 +1230,26 @@
         <v>300</v>
       </c>
       <c r="N12" s="3">
+        <v>300</v>
+      </c>
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
       </c>
       <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,26 +1417,29 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>300</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
         <v>300</v>
       </c>
       <c r="F14" s="3">
+        <v>300</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1445,25 +1465,25 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-6200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2400</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1480,8 +1500,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1489,29 +1509,32 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>200</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1522,10 +1545,10 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
         <v>400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>500</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
@@ -1543,7 +1566,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,141 +1683,145 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E17" s="3">
         <v>28200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>33900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>29300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>28300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>28800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>28900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>27800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>26600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>27300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>28000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>30200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>28200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>28700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1100</v>
       </c>
       <c r="K18" s="3">
         <v>1100</v>
@@ -1800,85 +1830,88 @@
         <v>1100</v>
       </c>
       <c r="M18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N18" s="3">
         <v>700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>800</v>
       </c>
       <c r="Z18" s="3">
         <v>800</v>
       </c>
       <c r="AA18" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="3">
         <v>700</v>
       </c>
       <c r="AF18" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,8 +1983,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1974,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -2027,31 +2061,34 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1600</v>
       </c>
       <c r="K21" s="3">
         <v>1600</v>
@@ -2060,90 +2097,93 @@
         <v>1600</v>
       </c>
       <c r="M21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>500</v>
       </c>
       <c r="AC21" s="3">
         <v>500</v>
       </c>
       <c r="AD21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -2158,7 +2198,7 @@
         <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -2188,25 +2228,25 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
-      </c>
-      <c r="W22" s="3">
-        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>300</v>
@@ -2215,7 +2255,7 @@
         <v>300</v>
       </c>
       <c r="AB22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
@@ -2236,7 +2276,7 @@
         <v>200</v>
       </c>
       <c r="AI22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ22" s="3">
         <v>100</v>
@@ -2247,201 +2287,207 @@
       <c r="AL22" s="3">
         <v>100</v>
       </c>
+      <c r="AM22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1000</v>
       </c>
       <c r="K23" s="3">
         <v>1000</v>
       </c>
       <c r="L23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>500</v>
       </c>
       <c r="AE23" s="3">
         <v>500</v>
       </c>
       <c r="AF23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>0</v>
-      </c>
       <c r="AK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="3">
         <v>200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="3">
         <v>100</v>
@@ -2450,25 +2496,28 @@
         <v>100</v>
       </c>
       <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,104 +2626,107 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>400</v>
       </c>
       <c r="AE26" s="3">
         <v>400</v>
       </c>
       <c r="AF26" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
         <v>0</v>
       </c>
@@ -2682,109 +2734,112 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="3">
         <v>100</v>
       </c>
+      <c r="AM26" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>400</v>
       </c>
       <c r="AE27" s="3">
         <v>400</v>
       </c>
       <c r="AF27" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
         <v>0</v>
       </c>
@@ -2792,13 +2847,16 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL27" s="3">
         <v>100</v>
       </c>
+      <c r="AM27" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2981,17 +3042,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2999,12 +3060,12 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-300</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,8 +3339,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3294,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3347,104 +3417,107 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>400</v>
       </c>
       <c r="AE33" s="3">
         <v>400</v>
       </c>
       <c r="AF33" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
@@ -3452,13 +3525,16 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="3">
         <v>100</v>
       </c>
+      <c r="AM33" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,104 +3643,107 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>400</v>
       </c>
       <c r="AE35" s="3">
         <v>400</v>
       </c>
       <c r="AF35" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
         <v>0</v>
       </c>
@@ -3672,128 +3751,134 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL35" s="3">
         <v>100</v>
       </c>
+      <c r="AM35" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,97 +3958,98 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
-      </c>
-      <c r="T41" s="3">
-        <v>400</v>
       </c>
       <c r="U41" s="3">
         <v>400</v>
       </c>
       <c r="V41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W41" s="3">
         <v>300</v>
       </c>
       <c r="X41" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y41" s="3">
         <v>700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>500</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>400</v>
       </c>
       <c r="AE41" s="3">
         <v>400</v>
       </c>
       <c r="AF41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AG41" s="3">
         <v>500</v>
@@ -3971,19 +4058,22 @@
         <v>500</v>
       </c>
       <c r="AI41" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AJ41" s="3">
         <v>200</v>
       </c>
       <c r="AK41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL41" s="3">
         <v>300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,236 +4182,245 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E43" s="3">
         <v>29100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>32500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>33800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>28500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>27900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>24300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>18600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>17300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>17500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E44" s="3">
         <v>20900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>22300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>21500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>21100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>21300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>21200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>20600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>17100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>14500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>15500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>15400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>14300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>16900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>16300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>15200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>14000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>13000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>18500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>21100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>21600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>21700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>20700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="E45" s="3">
+        <v>500</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
@@ -4344,196 +4443,202 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>2400</v>
       </c>
       <c r="T45" s="3">
         <v>2400</v>
       </c>
       <c r="U45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V45" s="3">
         <v>5200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2200</v>
-      </c>
-      <c r="X45" s="3">
-        <v>2400</v>
       </c>
       <c r="Y45" s="3">
         <v>2400</v>
       </c>
       <c r="Z45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA45" s="3">
         <v>3800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E46" s="3">
         <v>57300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>59100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>54900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>56500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>52800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>51800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>51100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>41000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>40800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>43600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>45500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>43300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>48300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>46800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>50500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>43300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>39100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>37800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>41800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>40300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>39500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,91 +4747,94 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E48" s="3">
         <v>13400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14500</v>
-      </c>
-      <c r="O48" s="3">
-        <v>14600</v>
       </c>
       <c r="P48" s="3">
         <v>14600</v>
       </c>
       <c r="Q48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="R48" s="3">
         <v>14800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14400</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>14700</v>
       </c>
       <c r="AA48" s="3">
         <v>14700</v>
       </c>
       <c r="AB48" s="3">
+        <v>14700</v>
+      </c>
+      <c r="AC48" s="3">
         <v>15300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10200</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>10100</v>
       </c>
       <c r="AE48" s="3">
         <v>10100</v>
@@ -4735,25 +4843,28 @@
         <v>10100</v>
       </c>
       <c r="AG48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AH48" s="3">
         <v>10200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>10300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4773,7 +4884,7 @@
         <v>200</v>
       </c>
       <c r="I49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J49" s="3">
         <v>300</v>
@@ -4782,7 +4893,7 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M49" s="3">
         <v>400</v>
@@ -4791,7 +4902,7 @@
         <v>400</v>
       </c>
       <c r="O49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P49" s="3">
         <v>500</v>
@@ -4803,28 +4914,28 @@
         <v>500</v>
       </c>
       <c r="S49" s="3">
+        <v>500</v>
+      </c>
+      <c r="T49" s="3">
         <v>1100</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1200</v>
       </c>
       <c r="U49" s="3">
         <v>1200</v>
       </c>
       <c r="V49" s="3">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="W49" s="3">
         <v>3600</v>
       </c>
       <c r="X49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="Y49" s="3">
         <v>3700</v>
       </c>
       <c r="Z49" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="AA49" s="3">
         <v>3800</v>
@@ -4833,37 +4944,40 @@
         <v>3800</v>
       </c>
       <c r="AC49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AD49" s="3">
         <v>3900</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>4000</v>
       </c>
       <c r="AE49" s="3">
         <v>4000</v>
       </c>
       <c r="AF49" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="AG49" s="3">
         <v>4100</v>
       </c>
       <c r="AH49" s="3">
-        <v>5100</v>
+        <v>4100</v>
       </c>
       <c r="AI49" s="3">
         <v>5100</v>
       </c>
       <c r="AJ49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AK49" s="3">
         <v>5200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,16 +5199,19 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
+      <c r="E52" s="3">
+        <v>100</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
@@ -5120,8 +5240,8 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -5129,17 +5249,17 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S52" s="3">
-        <v>400</v>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
+      <c r="U52" s="3">
+        <v>400</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
@@ -5150,8 +5270,8 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -5178,10 +5298,10 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
         <v>500</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>600</v>
       </c>
       <c r="AJ52" s="3">
         <v>600</v>
@@ -5190,10 +5310,13 @@
         <v>600</v>
       </c>
       <c r="AL52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AM52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E54" s="3">
         <v>73500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>72400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>76300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>67100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>61100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>63100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>65300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>69700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>53300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>52100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>57500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>55800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>55500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,123 +5622,127 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E57" s="3">
         <v>10600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13000</v>
-      </c>
-      <c r="U57" s="3">
-        <v>11200</v>
       </c>
       <c r="V57" s="3">
         <v>11200</v>
       </c>
       <c r="W57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="X57" s="3">
         <v>13500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>16400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>18100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>16900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>15700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>14800</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>15300</v>
       </c>
       <c r="AJ57" s="3">
         <v>15300</v>
       </c>
       <c r="AK57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AL57" s="3">
         <v>13800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E58" s="3">
         <v>1300</v>
@@ -5617,25 +5751,25 @@
         <v>1300</v>
       </c>
       <c r="G58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1400</v>
       </c>
       <c r="J58" s="3">
         <v>1400</v>
       </c>
       <c r="K58" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="L58" s="3">
         <v>1500</v>
       </c>
       <c r="M58" s="3">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="N58" s="3">
         <v>400</v>
@@ -5644,25 +5778,25 @@
         <v>400</v>
       </c>
       <c r="P58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1900</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1100</v>
       </c>
       <c r="W58" s="3">
         <v>1100</v>
@@ -5671,40 +5805,40 @@
         <v>1100</v>
       </c>
       <c r="Y58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1400</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1300</v>
       </c>
       <c r="AG58" s="3">
         <v>1300</v>
       </c>
       <c r="AH58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI58" s="3">
         <v>1200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>1600</v>
       </c>
       <c r="AK58" s="3">
         <v>1600</v>
@@ -5712,100 +5846,103 @@
       <c r="AL58" s="3">
         <v>1600</v>
       </c>
+      <c r="AM58" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E59" s="3">
         <v>5000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5100</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>5000</v>
       </c>
       <c r="AH59" s="3">
         <v>5000</v>
@@ -5814,236 +5951,245 @@
         <v>5000</v>
       </c>
       <c r="AJ59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AK59" s="3">
         <v>3900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E60" s="3">
         <v>20700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21400</v>
-      </c>
-      <c r="F60" s="3">
-        <v>23300</v>
       </c>
       <c r="G60" s="3">
         <v>23300</v>
       </c>
       <c r="H60" s="3">
+        <v>23300</v>
+      </c>
+      <c r="I60" s="3">
         <v>25700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>18200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>22200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>25600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>28100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>24900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>23100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>20900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>21400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>20800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>20300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E61" s="3">
         <v>19700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10600</v>
-      </c>
-      <c r="W61" s="3">
-        <v>14900</v>
       </c>
       <c r="X61" s="3">
         <v>14900</v>
       </c>
       <c r="Y61" s="3">
+        <v>14900</v>
+      </c>
+      <c r="Z61" s="3">
         <v>14700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6051,10 +6197,10 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
+        <v>300</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>400</v>
@@ -6066,7 +6212,7 @@
         <v>400</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
@@ -6075,85 +6221,88 @@
         <v>100</v>
       </c>
       <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
         <v>7600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9500</v>
-      </c>
-      <c r="U62" s="3">
-        <v>9000</v>
       </c>
       <c r="V62" s="3">
         <v>9000</v>
       </c>
       <c r="W62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="X62" s="3">
         <v>4200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>100</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>200</v>
       </c>
       <c r="AE62" s="3">
         <v>200</v>
       </c>
       <c r="AF62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG62" s="3">
         <v>100</v>
       </c>
       <c r="AH62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI62" s="3">
         <v>400</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>600</v>
       </c>
       <c r="AJ62" s="3">
         <v>600</v>
       </c>
       <c r="AK62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL62" s="3">
         <v>700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E66" s="3">
         <v>40700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>44900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>44600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>41600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>38900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>41100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>43000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>41400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>48700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>36100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>34900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>32500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>32300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>35200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>33600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>33200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>300</v>
       </c>
+      <c r="AM70" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,103 +7243,106 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E72" s="3">
         <v>16100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AH72" s="3">
-        <v>6300</v>
       </c>
       <c r="AI72" s="3">
         <v>6300</v>
@@ -7180,10 +7354,13 @@
         <v>6300</v>
       </c>
       <c r="AL72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AM72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E76" s="3">
         <v>32600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21900</v>
-      </c>
-      <c r="W76" s="3">
-        <v>19800</v>
       </c>
       <c r="X76" s="3">
         <v>19800</v>
       </c>
       <c r="Y76" s="3">
+        <v>19800</v>
+      </c>
+      <c r="Z76" s="3">
         <v>19700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22100</v>
-      </c>
-      <c r="AI76" s="3">
-        <v>22000</v>
       </c>
       <c r="AJ76" s="3">
         <v>22000</v>
       </c>
       <c r="AK76" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AL76" s="3">
         <v>22100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,219 +7921,225 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>400</v>
       </c>
       <c r="AE81" s="3">
         <v>400</v>
       </c>
       <c r="AF81" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
         <v>0</v>
       </c>
@@ -7952,13 +8147,16 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL81" s="3">
         <v>100</v>
       </c>
+      <c r="AM81" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8006,7 +8205,7 @@
         <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>500</v>
@@ -8018,7 +8217,7 @@
         <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
@@ -8027,7 +8226,7 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
@@ -8042,22 +8241,22 @@
         <v>500</v>
       </c>
       <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>500</v>
       </c>
       <c r="U83" s="3">
         <v>500</v>
       </c>
       <c r="V83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W83" s="3">
         <v>600</v>
@@ -8072,13 +8271,13 @@
         <v>600</v>
       </c>
       <c r="AA83" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB83" s="3">
         <v>500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>600</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>500</v>
       </c>
       <c r="AD83" s="3">
         <v>500</v>
@@ -8087,7 +8286,7 @@
         <v>500</v>
       </c>
       <c r="AF83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AG83" s="3">
         <v>600</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>600</v>
       </c>
+      <c r="AM83" s="3">
+        <v>600</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,85 +9027,86 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-500</v>
       </c>
       <c r="M91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-200</v>
       </c>
       <c r="W91" s="3">
         <v>-200</v>
       </c>
       <c r="X91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-400</v>
       </c>
       <c r="AC91" s="3">
         <v>-400</v>
@@ -8894,13 +9115,13 @@
         <v>-400</v>
       </c>
       <c r="AE91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AF91" s="3">
         <v>-300</v>
       </c>
       <c r="AG91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AH91" s="3">
         <v>-200</v>
@@ -8912,13 +9133,16 @@
         <v>-200</v>
       </c>
       <c r="AK91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AL91" s="3">
         <v>-300</v>
       </c>
+      <c r="AM91" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,85 +9364,88 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>-300</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-200</v>
       </c>
       <c r="J94" s="3">
         <v>-200</v>
       </c>
       <c r="K94" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-500</v>
       </c>
       <c r="M94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-400</v>
       </c>
       <c r="AC94" s="3">
         <v>-400</v>
@@ -9224,7 +9454,7 @@
         <v>-400</v>
       </c>
       <c r="AE94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AF94" s="3">
         <v>-300</v>
@@ -9233,22 +9463,25 @@
         <v>-300</v>
       </c>
       <c r="AH94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AI94" s="3">
         <v>-200</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AK94" s="3">
         <v>400</v>
-      </c>
-      <c r="AK94" s="3">
-        <v>-300</v>
       </c>
       <c r="AL94" s="3">
         <v>-300</v>
       </c>
+      <c r="AM94" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,118 +9970,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-100</v>
       </c>
       <c r="X100" s="3">
         <v>-100</v>
       </c>
       <c r="Y100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-300</v>
       </c>
       <c r="AG100" s="3">
         <v>-300</v>
       </c>
       <c r="AH100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI100" s="3">
         <v>1400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9858,11 +10107,11 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
@@ -9878,11 +10127,11 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
@@ -9890,11 +10139,11 @@
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
+      <c r="T101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
@@ -9902,8 +10151,8 @@
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -9924,11 +10173,11 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -9941,120 +10190,126 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>8</v>
+      <c r="AK101" s="3">
+        <v>0</v>
       </c>
       <c r="AL101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-300</v>
       </c>
       <c r="F102" s="3">
         <v>-300</v>
       </c>
       <c r="G102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSYS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>NSYS</t>
   </si>
@@ -656,518 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F8" s="3">
         <v>30500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>30700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>26900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>28600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>31400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>33900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>34200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>36100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>33400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>35000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>34900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>35600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>35300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>32500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>30700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>33500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>29500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>52300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>22100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>23800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>26400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>26500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>27400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>30800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>30100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>27300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>28200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>28800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>29600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>28500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>26400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>25600</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>28300</v>
-      </c>
-      <c r="AK8" s="3">
-        <v>30100</v>
       </c>
       <c r="AL8" s="3">
         <v>28300</v>
       </c>
       <c r="AM8" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AO8" s="3">
         <v>29000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F9" s="3">
         <v>25500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>25800</v>
-      </c>
-      <c r="F9" s="3">
-        <v>23800</v>
       </c>
       <c r="G9" s="3">
         <v>25800</v>
       </c>
       <c r="H9" s="3">
+        <v>23800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>25800</v>
+      </c>
+      <c r="J9" s="3">
         <v>27600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>29300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>28800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>29200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>28100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>29500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>29400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>30500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>28900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>27500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>26700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>30800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>21400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>47100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>20500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>22100</v>
-      </c>
-      <c r="X9" s="3">
-        <v>24400</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>24000</v>
       </c>
       <c r="Z9" s="3">
         <v>24400</v>
       </c>
       <c r="AA9" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>24400</v>
+      </c>
+      <c r="AC9" s="3">
         <v>27200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>26400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>25000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>25200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>25700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>26200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>24700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>23400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>23400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>24800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>26800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>25200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>25500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F10" s="3">
         <v>5000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>6800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>5100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>6400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>8100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>3600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>3800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>3000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>3500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>3300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>3100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>3500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1250,29 +1277,29 @@
         <v>300</v>
       </c>
       <c r="P12" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>300</v>
+      </c>
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1324,8 +1351,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,35 +1473,41 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1478,11 +1517,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1491,28 +1530,28 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-6200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>2400</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1526,38 +1565,44 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>900</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>200</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1574,13 +1619,13 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
         <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1595,10 +1640,10 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1672,8 +1717,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F17" s="3">
         <v>29500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>29900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>28200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>29500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>31700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>33500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>33100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>33400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>32200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>33900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>33800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>34900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>33300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>31500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>30500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>28200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>24500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>54000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>24200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>27600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>23700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>26400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>27000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>30000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>29300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>28500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>28300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>28800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>28900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>27800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>26600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>27300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>28000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>30200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>28200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>28700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
+        <v>900</v>
+      </c>
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1100</v>
       </c>
       <c r="N18" s="3">
         <v>1100</v>
       </c>
       <c r="O18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
         <v>700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2050,10 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,11 +2090,11 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2048,17 +2115,17 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -2101,124 +2168,136 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>3200</v>
       </c>
       <c r="L21" s="3">
         <v>1600</v>
       </c>
       <c r="M21" s="3">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="N21" s="3">
         <v>1600</v>
       </c>
       <c r="O21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>5700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>5500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2226,13 +2305,13 @@
         <v>300</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
-        <v>200</v>
-      </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
@@ -2244,10 +2323,10 @@
         <v>200</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -2274,7 +2353,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
@@ -2283,28 +2362,28 @@
         <v>200</v>
       </c>
       <c r="X22" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
       </c>
       <c r="Z22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="AA22" s="3">
-        <v>300</v>
-      </c>
       <c r="AB22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>300</v>
       </c>
       <c r="AD22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF22" s="3">
         <v>200</v>
@@ -2322,10 +2401,10 @@
         <v>200</v>
       </c>
       <c r="AK22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM22" s="3">
         <v>100</v>
@@ -2333,240 +2412,258 @@
       <c r="AN22" s="3">
         <v>100</v>
       </c>
+      <c r="AO22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>700</v>
+      </c>
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>2600</v>
       </c>
       <c r="L23" s="3">
         <v>1000</v>
       </c>
       <c r="M23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>4800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-200</v>
       </c>
-      <c r="AL23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="3">
         <v>200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1100</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
       </c>
       <c r="Q24" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="R24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>1200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH24" s="3">
         <v>100</v>
       </c>
       <c r="AI24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ24" s="3">
         <v>100</v>
       </c>
       <c r="AK24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM24" s="3">
         <v>-200</v>
       </c>
-      <c r="AL24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>5000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3">
-        <v>0</v>
-      </c>
       <c r="AL26" s="3">
         <v>0</v>
       </c>
       <c r="AM26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3">
         <v>100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3">
-        <v>0</v>
-      </c>
       <c r="AL27" s="3">
         <v>0</v>
       </c>
       <c r="AM27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3">
         <v>100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3109,33 +3230,33 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3510,14 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,11 +3554,11 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3440,17 +3579,17 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -3493,124 +3632,136 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3">
-        <v>0</v>
-      </c>
       <c r="AL33" s="3">
         <v>0</v>
       </c>
       <c r="AM33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3">
         <v>100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="3">
-        <v>0</v>
-      </c>
       <c r="AL35" s="3">
         <v>0</v>
       </c>
       <c r="AM35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3">
         <v>100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4217,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F41" s="3">
         <v>1300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>900</v>
       </c>
       <c r="H41" s="3">
         <v>1200</v>
       </c>
       <c r="I41" s="3">
+        <v>900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
-      </c>
-      <c r="N41" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1000</v>
       </c>
       <c r="P41" s="3">
         <v>1300</v>
       </c>
       <c r="Q41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>600</v>
-      </c>
-      <c r="T41" s="3">
-        <v>400</v>
-      </c>
-      <c r="U41" s="3">
-        <v>700</v>
       </c>
       <c r="V41" s="3">
         <v>400</v>
       </c>
       <c r="W41" s="3">
+        <v>700</v>
+      </c>
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>400</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>200</v>
       </c>
       <c r="AC41" s="3">
         <v>400</v>
       </c>
       <c r="AD41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>400</v>
-      </c>
-      <c r="AH41" s="3">
-        <v>500</v>
-      </c>
-      <c r="AI41" s="3">
-        <v>500</v>
       </c>
       <c r="AJ41" s="3">
         <v>500</v>
       </c>
       <c r="AK41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM41" s="3">
         <v>200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,258 +4457,276 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F43" s="3">
         <v>34100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>32800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>29100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>28700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>31600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>32500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>30200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>33800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>28100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>29000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>29700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>28600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>30600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>30700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>28000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>28500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>27300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>24800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>20500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>21500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>23400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>25600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>27000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>26200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>27300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>27900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>31700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>26500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>26100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>25900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>24300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>18600</v>
-      </c>
-      <c r="AK43" s="3">
-        <v>17500</v>
-      </c>
-      <c r="AL43" s="3">
-        <v>17300</v>
       </c>
       <c r="AM43" s="3">
         <v>17500</v>
       </c>
       <c r="AN43" s="3">
+        <v>17300</v>
+      </c>
+      <c r="AO43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="AP43" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F44" s="3">
         <v>18400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>18600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>20900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>21600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>22300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>22800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>23000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>21700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>21500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>21100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>21300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>22400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>23600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>23000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>21200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>19400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>20600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>18300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>17100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>13900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>14500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>15500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>15400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>14300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>16900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>16300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>16000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>17000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>15200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>14000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>13000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>21100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>21600</v>
-      </c>
-      <c r="AL44" s="3">
-        <v>21700</v>
-      </c>
-      <c r="AM44" s="3">
-        <v>20700</v>
       </c>
       <c r="AN44" s="3">
         <v>21700</v>
       </c>
+      <c r="AO44" s="3">
+        <v>20700</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>21700</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4548,202 +4745,214 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>3200</v>
       </c>
       <c r="T45" s="3">
         <v>2800</v>
       </c>
       <c r="U45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W45" s="3">
         <v>2400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>5200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>3800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>1600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>1400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>1200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>1000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>56200</v>
+      </c>
+      <c r="F46" s="3">
         <v>59200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>58300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>57300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>55300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>60300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>59200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>59100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>58800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>52600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>54400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>55600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>54900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>58100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>56500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>52800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>51800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>51100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>46200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>40400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>41000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>40800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>43600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>45500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>43300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>48300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>46800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>50500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>45900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>43300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>41800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>39100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>37800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>41800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>40700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>40300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>39500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,11 +4989,11 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4858,124 +5067,136 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F48" s="3">
         <v>12600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>13900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>14300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>13500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>13400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>13100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>13700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>14100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>14500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>14600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>14600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>14900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>15100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>15500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>15400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>15600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>13800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>14000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>14400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>14700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>14700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>15300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>10200</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>10100</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>10100</v>
       </c>
       <c r="AH48" s="3">
         <v>10100</v>
       </c>
       <c r="AI48" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="AJ48" s="3">
         <v>10100</v>
       </c>
       <c r="AK48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AM48" s="3">
         <v>9500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>9700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>10300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5001,28 +5222,28 @@
         <v>200</v>
       </c>
       <c r="K49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M49" s="3">
         <v>300</v>
       </c>
       <c r="N49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P49" s="3">
         <v>400</v>
       </c>
       <c r="Q49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S49" s="3">
         <v>500</v>
@@ -5031,58 +5252,58 @@
         <v>500</v>
       </c>
       <c r="U49" s="3">
+        <v>500</v>
+      </c>
+      <c r="V49" s="3">
+        <v>500</v>
+      </c>
+      <c r="W49" s="3">
         <v>1100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>3700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3700</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>3800</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>3800</v>
       </c>
       <c r="AD49" s="3">
         <v>3800</v>
       </c>
       <c r="AE49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AG49" s="3">
         <v>3900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>4000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>4000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>4100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>5100</v>
-      </c>
-      <c r="AK49" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>5200</v>
       </c>
       <c r="AM49" s="3">
         <v>5100</v>
@@ -5090,8 +5311,14 @@
       <c r="AN49" s="3">
         <v>5200</v>
       </c>
+      <c r="AO49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,26 +5555,32 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5366,41 +5605,41 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -5424,22 +5663,28 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
         <v>500</v>
-      </c>
-      <c r="AK52" s="3">
-        <v>600</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>600</v>
       </c>
       <c r="AM52" s="3">
         <v>600</v>
       </c>
       <c r="AN52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AP52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>71900</v>
+      </c>
+      <c r="F54" s="3">
         <v>74800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>74800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>73500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>72400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>77000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>76300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>75500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>75100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>66000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>68400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>70100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>69500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>73100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>71500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>67900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>67100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>66500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>62800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>57500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>57600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>60000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>61100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>63100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>61400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>66800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>65300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>69700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>60000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>57400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>55900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>53300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>52100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>57500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>55900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>55800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>55500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,240 +6013,254 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F57" s="3">
         <v>11700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>12300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>15200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>15900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>13100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>15300</v>
       </c>
       <c r="N57" s="3">
         <v>13100</v>
       </c>
       <c r="O57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="P57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>14800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>14700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>14100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>14000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>12700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>14100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>12800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>13000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>11200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>11200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>13500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>16400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>14000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>18400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>16800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>21100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>18100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>16900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>15700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>12100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>14800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>15300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>15300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>13800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F58" s="3">
         <v>13600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1300</v>
       </c>
       <c r="H58" s="3">
         <v>1300</v>
       </c>
       <c r="I58" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="J58" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="K58" s="3">
         <v>1400</v>
       </c>
       <c r="L58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1500</v>
-      </c>
-      <c r="O58" s="3">
-        <v>400</v>
-      </c>
-      <c r="P58" s="3">
-        <v>400</v>
       </c>
       <c r="Q58" s="3">
         <v>400</v>
       </c>
       <c r="R58" s="3">
+        <v>400</v>
+      </c>
+      <c r="S58" s="3">
+        <v>400</v>
+      </c>
+      <c r="T58" s="3">
         <v>500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>9800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>11400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1900</v>
-      </c>
-      <c r="X58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>1100</v>
       </c>
       <c r="Z58" s="3">
         <v>1100</v>
       </c>
       <c r="AA58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>900</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>1200</v>
       </c>
       <c r="AD58" s="3">
         <v>900</v>
       </c>
       <c r="AE58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG58" s="3">
         <v>1100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>1200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>1100</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AM58" s="3">
-        <v>1600</v>
       </c>
       <c r="AN58" s="3">
         <v>1600</v>
       </c>
+      <c r="AO58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AP58" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5995,367 +6268,385 @@
         <v>4700</v>
       </c>
       <c r="E59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G59" s="3">
         <v>5200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>11200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>9700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>10200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>9000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>8900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>7100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>6400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>5900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>7300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>6400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>7200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>6300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>6700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>6100</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>5600</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>5000</v>
       </c>
       <c r="AG59" s="3">
         <v>5600</v>
       </c>
       <c r="AH59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>5100</v>
-      </c>
-      <c r="AI59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AJ59" s="3">
-        <v>5000</v>
       </c>
       <c r="AK59" s="3">
         <v>5000</v>
       </c>
       <c r="AL59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AM59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AN59" s="3">
         <v>3900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>4900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F60" s="3">
         <v>33600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>21600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>20700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>21400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>23300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>23300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>25700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>26600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>23200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>24400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>27400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>26400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>26600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>24300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>24700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>22300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>32900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>31400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>22700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>19500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>18200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>21900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>23800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>22200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>25600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>24800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>28100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>24900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>23100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>22700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>18400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>20900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>21400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>20800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>20300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F61" s="3">
         <v>7500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>19500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>19700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>16700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>17500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>16400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>13300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>14500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>13600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>10500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>12100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>9900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>8200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>10300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>10600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>14900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>14900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>14700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>16900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>16500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>15700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>13800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>12800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>12100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>14000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>13900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>11500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>12000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>12200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>300</v>
       </c>
       <c r="G62" s="3">
+        <v>300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>300</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
@@ -6364,94 +6655,100 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
       <c r="O62" s="3">
+        <v>100</v>
+      </c>
+      <c r="P62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>7600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>7900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>8500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>8800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>8900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>9300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>9500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>9000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>9000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>4200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>4500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>4600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>4800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>4900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>37400</v>
+      </c>
+      <c r="F66" s="3">
         <v>41400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>41400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>40700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>38400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>41300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>40100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>39400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>39800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>35300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>38900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>41200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>41500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>44900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>44600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>41600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>41000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>45500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>45400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>40300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>38900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>37800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>41100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>43000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>41400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>47100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>46100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>48700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>38900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>36100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>34900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>32500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>32300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>35200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>33600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>33500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>33200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>300</v>
       </c>
+      <c r="AO70" s="3">
+        <v>300</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,112 +7761,118 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F72" s="3">
         <v>16200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>16400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>16100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>17400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>18900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>19600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>19400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>18700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>14300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>13100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>12500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>11800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>12200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>10700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>10000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>9800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>4900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6200</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>4200</v>
-      </c>
-      <c r="Z72" s="3">
-        <v>4300</v>
       </c>
       <c r="AA72" s="3">
         <v>4200</v>
       </c>
       <c r="AB72" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AC72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AD72" s="3">
         <v>3900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>3500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>5400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>5600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>5300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>4900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>3900</v>
-      </c>
-      <c r="AJ72" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AK72" s="3">
-        <v>6300</v>
       </c>
       <c r="AL72" s="3">
         <v>6300</v>
@@ -7534,10 +7881,16 @@
         <v>6300</v>
       </c>
       <c r="AN72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AO72" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AP72" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>34300</v>
+      </c>
+      <c r="F76" s="3">
         <v>33100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>33100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>32600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>33800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>35400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>35900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>35800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>35100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>30500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>29200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>28700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>27800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>27900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>26700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>26100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>25900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>20800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>17200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>16900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>18500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>21900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>19800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>19800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>19700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>19400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>19000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>20700</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>20800</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>21000</v>
       </c>
       <c r="AG76" s="3">
         <v>20800</v>
       </c>
       <c r="AH76" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AI76" s="3">
+        <v>20800</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>20500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>19600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>22100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>22000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>22000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>22100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
+        <v>900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK81" s="3">
-        <v>0</v>
-      </c>
       <c r="AL81" s="3">
         <v>0</v>
       </c>
       <c r="AM81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="3">
         <v>100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,25 +8790,27 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
@@ -8422,19 +8819,19 @@
         <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
       </c>
       <c r="N83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
@@ -8446,25 +8843,25 @@
         <v>500</v>
       </c>
       <c r="S83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T83" s="3">
         <v>500</v>
       </c>
       <c r="U83" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="V83" s="3">
         <v>500</v>
       </c>
       <c r="W83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3">
-        <v>600</v>
-      </c>
       <c r="Y83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z83" s="3">
         <v>600</v>
@@ -8476,7 +8873,7 @@
         <v>600</v>
       </c>
       <c r="AC83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AD83" s="3">
         <v>600</v>
@@ -8485,16 +8882,16 @@
         <v>500</v>
       </c>
       <c r="AF83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AG83" s="3">
         <v>500</v>
       </c>
       <c r="AH83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AI83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AJ83" s="3">
         <v>600</v>
@@ -8511,8 +8908,14 @@
       <c r="AN83" s="3">
         <v>600</v>
       </c>
+      <c r="AO83" s="3">
+        <v>600</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>600</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>4400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>2200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>1700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9688,10 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9261,34 +9702,34 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-700</v>
       </c>
       <c r="P91" s="3">
         <v>-500</v>
@@ -9300,58 +9741,58 @@
         <v>-500</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="T91" s="3">
         <v>-500</v>
       </c>
       <c r="U91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W91" s="3">
         <v>-700</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>-200</v>
       </c>
       <c r="Y91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-400</v>
       </c>
       <c r="AF91" s="3">
         <v>-400</v>
       </c>
       <c r="AG91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-200</v>
       </c>
       <c r="AK91" s="3">
         <v>-200</v>
@@ -9360,13 +9801,19 @@
         <v>-200</v>
       </c>
       <c r="AM91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AN91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,46 +10050,52 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>300</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>-300</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-700</v>
       </c>
       <c r="P94" s="3">
         <v>-500</v>
@@ -9648,73 +10107,79 @@
         <v>-500</v>
       </c>
       <c r="S94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>5800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-400</v>
       </c>
       <c r="AF94" s="3">
         <v>-400</v>
       </c>
       <c r="AG94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AH94" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AI94" s="3">
         <v>-300</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10220,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,11 +10260,11 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10338,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,124 +10704,136 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-3200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>3700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>1600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>1400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10362,14 +10859,14 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
@@ -10382,35 +10879,35 @@
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -10428,14 +10925,14 @@
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
@@ -10445,14 +10942,20 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
-      <c r="AM101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP101" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10460,111 +10963,117 @@
         <v>600</v>
       </c>
       <c r="E102" s="3">
+        <v>400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>600</v>
+      </c>
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>0</v>
       </c>
     </row>
